--- a/contact/beimeifx/north_america_game_publishers.xlsx
+++ b/contact/beimeifx/north_america_game_publishers.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targets" sheetId="1" r:id="R4f08fe2125af4c1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targets" sheetId="1" r:id="Rc618f9734af440ae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -720,18 +720,23 @@
     <x:col min="3" max="3" width="25.559999465942383" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="9.779999732971191" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18.889999389648438" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="26.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="17.780000686645508" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="40" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="40" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="24.440000534057617" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="25.559999465942383" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="24.440000534057617" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="7.78000020980835" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="33.33000183105469" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="35.560001373291016" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="33.33000183105469" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="31.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18.889999389648438" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="40" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="40" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="24.440000534057617" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="25.559999465942383" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="25.559999465942383" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="25.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="24.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="7.78000020980835" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="33.33000183105469" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="24.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="24.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="24.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="24.440000534057617" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -754,37 +759,52 @@
         <x:v>website</x:v>
       </x:c>
       <x:c r="G1" s="83" t="str">
+        <x:v>company_scale</x:v>
+      </x:c>
+      <x:c r="H1" s="83" t="str">
+        <x:v>representative_works</x:v>
+      </x:c>
+      <x:c r="I1" s="83" t="str">
+        <x:v>contact_email</x:v>
+      </x:c>
+      <x:c r="J1" s="83" t="str">
+        <x:v>email_note</x:v>
+      </x:c>
+      <x:c r="K1" s="83" t="str">
         <x:v>archetype</x:v>
       </x:c>
-      <x:c r="H1" s="83" t="str">
+      <x:c r="L1" s="83" t="str">
         <x:v>industry_position</x:v>
       </x:c>
-      <x:c r="I1" s="83" t="str">
+      <x:c r="M1" s="83" t="str">
         <x:v>family_island_fit</x:v>
       </x:c>
-      <x:c r="J1" s="83" t="str">
+      <x:c r="N1" s="83" t="str">
         <x:v>deal_types</x:v>
       </x:c>
-      <x:c r="K1" s="83" t="str">
+      <x:c r="O1" s="83" t="str">
         <x:v>best_entry</x:v>
       </x:c>
-      <x:c r="L1" s="83" t="str">
+      <x:c r="P1" s="83" t="str">
         <x:v>contact</x:v>
       </x:c>
-      <x:c r="M1" s="83" t="str">
+      <x:c r="Q1" s="83" t="str">
         <x:v>score</x:v>
       </x:c>
-      <x:c r="N1" s="83" t="str">
+      <x:c r="R1" s="83" t="str">
         <x:v>next_step</x:v>
       </x:c>
-      <x:c r="O1" s="83" t="str">
+      <x:c r="S1" s="83" t="str">
         <x:v>source_1</x:v>
       </x:c>
-      <x:c r="P1" s="83" t="str">
+      <x:c r="T1" s="83" t="str">
         <x:v>source_2</x:v>
       </x:c>
-      <x:c r="Q1" s="84" t="str">
+      <x:c r="U1" s="83" t="str">
         <x:v>source_3</x:v>
+      </x:c>
+      <x:c r="V1" s="84" t="str">
+        <x:v>source_4</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="36" hidden="0" customHeight="1">
@@ -807,37 +827,52 @@
         <x:v>https://www.tiltingpoint.com/</x:v>
       </x:c>
       <x:c r="G2" s="44" t="str">
+        <x:v>官网披露 portfolio 80+ titles；全球工作室覆盖 Montreal、New York、Barcelona；移动发行/UA Fund 型中上游玩家。</x:v>
+      </x:c>
+      <x:c r="H2" s="44" t="str">
+        <x:v>Avatar: Realms Collide, SpongeBob: Krusty Cook-Off, Star Trek: Timelines, Cypher 007, Warhammer: Chaos &amp; Conquest</x:v>
+      </x:c>
+      <x:c r="I2" s="44" t="str">
+        <x:v>hello@tiltingpoint.com; press@tiltingpoint.com</x:v>
+      </x:c>
+      <x:c r="J2" s="44" t="str">
+        <x:v>官网 Contact 页公开：商务/一般咨询用 hello@；媒体用 press@。</x:v>
+      </x:c>
+      <x:c r="K2" s="44" t="str">
         <x:v>益世界式发行/增长伙伴</x:v>
       </x:c>
-      <x:c r="H2" s="44" t="str">
+      <x:c r="L2" s="44" t="str">
         <x:v>北美移动游戏发行服务商里最接近益世界画像的一类：不是平台巨头，但在外部项目发行、UA、LiveOps、IP合作和资金支持上有明确能力。</x:v>
       </x:c>
-      <x:c r="I2" s="44" t="str">
+      <x:c r="M2" s="44" t="str">
         <x:v>适合把项目包装为已在美国验证 CPI/留存的休闲冒险/模拟经营外部项目，先谈发行、UA funding、MG 或带投资条款的合作。</x:v>
       </x:c>
-      <x:c r="J2" s="44" t="str">
+      <x:c r="N2" s="44" t="str">
         <x:v>发行/MG；UA funding；战略投资；项目/团队收购讨论</x:v>
       </x:c>
-      <x:c r="K2" s="44" t="str">
+      <x:c r="O2" s="44" t="str">
         <x:v>Publishing / Business Development / Corporate Development</x:v>
       </x:c>
-      <x:c r="L2" s="44" t="str">
+      <x:c r="P2" s="44" t="str">
         <x:v>官网 contact / LinkedIn 公司页 / BD warm intro</x:v>
       </x:c>
-      <x:c r="M2" s="89" t="str">
+      <x:c r="Q2" s="89" t="str">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="N2" s="44" t="str">
+      <x:c r="R2" s="44" t="str">
         <x:v>第一波优先触达。邮件标题突出 US-tested、casual adventure/simulation、CPI &amp; retention signals。</x:v>
       </x:c>
-      <x:c r="O2" s="44" t="str">
+      <x:c r="S2" s="44" t="str">
         <x:v>https://www.tiltingpoint.com/</x:v>
       </x:c>
-      <x:c r="P2" s="44" t="str">
+      <x:c r="T2" s="44" t="str">
         <x:v>https://www.tiltingpoint.com/services/</x:v>
       </x:c>
-      <x:c r="Q2" s="45" t="str">
+      <x:c r="U2" s="44" t="str">
         <x:v>https://www.pocketgamer.biz/the-top-50-mobile-game-makers-of-2024/</x:v>
+      </x:c>
+      <x:c r="V2" s="45" t="str">
+        <x:v>https://www.tiltingpoint.com/contact/</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="36" hidden="0" customHeight="1">
@@ -860,37 +895,52 @@
         <x:v>https://www.jamcity.com/</x:v>
       </x:c>
       <x:c r="G3" s="44" t="str">
+        <x:v>官网披露 $4B+ aggregate lifetime bookings、nearly 1.5B downloads；LinkedIn 显示约 501-1,000 人。</x:v>
+      </x:c>
+      <x:c r="H3" s="44" t="str">
+        <x:v>Cookie Jam, Panda Pop, Harry Potter: Hogwarts Mystery, Disney Emoji Blitz, Family Guy: The Quest for Stuff, Disney Magic Match 3D</x:v>
+      </x:c>
+      <x:c r="I3" s="44" t="str">
+        <x:v>pr@jamcity.com; privacy@jamcity.com</x:v>
+      </x:c>
+      <x:c r="J3" s="44" t="str">
+        <x:v>官网公开媒体邮箱 pr@；未找到公开 BD/Publishing 邮箱，商务建议 LinkedIn/warm intro 并行。</x:v>
+      </x:c>
+      <x:c r="K3" s="44" t="str">
         <x:v>三七式研运发行公司</x:v>
       </x:c>
-      <x:c r="H3" s="44" t="str">
+      <x:c r="L3" s="44" t="str">
         <x:v>北美非平台型移动游戏开发发行商的中上游代表，强在休闲、IP、长线运营和移动端发行，不是 Scopely/Zynga 那种绝对巨头。</x:v>
       </x:c>
-      <x:c r="I3" s="44" t="str">
+      <x:c r="M3" s="44" t="str">
         <x:v>其 Cookie Jam、Panda Pop、Disney Emoji Blitz、Harry Potter 等产品线与休闲/轻中度移动用户重合度高。</x:v>
       </x:c>
-      <x:c r="J3" s="44" t="str">
+      <x:c r="N3" s="44" t="str">
         <x:v>发行合作；联合开发；项目收购；团队收购；少数股权投资可能性</x:v>
       </x:c>
-      <x:c r="K3" s="44" t="str">
+      <x:c r="O3" s="44" t="str">
         <x:v>Corporate Development / Publishing / Studio Leadership</x:v>
       </x:c>
-      <x:c r="L3" s="44" t="str">
+      <x:c r="P3" s="44" t="str">
         <x:v>官网 contact / LinkedIn / 洛杉矶游戏圈转介绍</x:v>
       </x:c>
-      <x:c r="M3" s="89" t="str">
+      <x:c r="Q3" s="89" t="str">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="N3" s="44" t="str">
+      <x:c r="R3" s="44" t="str">
         <x:v>作为三七互娱式对标重点触达，强调已验证美国市场和后续内容/LiveOps路线。</x:v>
       </x:c>
-      <x:c r="O3" s="44" t="str">
+      <x:c r="S3" s="44" t="str">
         <x:v>https://www.jamcity.com/</x:v>
       </x:c>
-      <x:c r="P3" s="44" t="str">
+      <x:c r="T3" s="44" t="str">
         <x:v>https://www.jamcity.com/games/</x:v>
       </x:c>
-      <x:c r="Q3" s="45" t="str">
+      <x:c r="U3" s="44" t="str">
         <x:v>https://www.pocketgamer.biz/the-top-50-mobile-game-makers-of-2024/</x:v>
+      </x:c>
+      <x:c r="V3" s="45" t="str">
+        <x:v>https://www.jamcity.com/press</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="36" hidden="0" customHeight="1">
@@ -913,37 +963,52 @@
         <x:v>https://www.eastsidegamesgroup.com/</x:v>
       </x:c>
       <x:c r="G4" s="44" t="str">
+        <x:v>上市公司；2025 全年收入约 CAD 77.6M；公开资料显示约 120 人；Vancouver HQ。</x:v>
+      </x:c>
+      <x:c r="H4" s="44" t="str">
+        <x:v>Trailer Park Boys: Greasy Money, RuPaul's Drag Race Superstar, Doctor Who: Lost in Time, Milk Farm Idle Tycoon, Bud Farm 系列</x:v>
+      </x:c>
+      <x:c r="I4" s="44" t="str">
+        <x:v>info@eastsidegamesgroup.com; ir@eastsidegamesgroup.com; jason@eastsidegamesgroup.com</x:v>
+      </x:c>
+      <x:c r="J4" s="44" t="str">
+        <x:v>官网 Contact 页公开 info/IR/M&amp;A 邮箱；M&amp;A 可优先 jason@。</x:v>
+      </x:c>
+      <x:c r="K4" s="44" t="str">
         <x:v>三七/益世界混合型</x:v>
       </x:c>
-      <x:c r="H4" s="44" t="str">
+      <x:c r="L4" s="44" t="str">
         <x:v>加拿大上市移动游戏集团，体量低于北美头部巨头，但具备自研、发行、技术平台和并购整合经验，适合作为中上游买方。</x:v>
       </x:c>
-      <x:c r="I4" s="44" t="str">
+      <x:c r="M4" s="44" t="str">
         <x:v>偏长线 F2P、IP/品牌合作和休闲移动运营，对已验证数据的小团队项目有一定战略可读性。</x:v>
       </x:c>
-      <x:c r="J4" s="44" t="str">
+      <x:c r="N4" s="44" t="str">
         <x:v>发行；联合开发；战略投资；资产/团队收购</x:v>
       </x:c>
-      <x:c r="K4" s="44" t="str">
+      <x:c r="O4" s="44" t="str">
         <x:v>Publishing / Corporate Development / CEO office</x:v>
       </x:c>
-      <x:c r="L4" s="44" t="str">
+      <x:c r="P4" s="44" t="str">
         <x:v>官网 inquiry / investor relations / LinkedIn</x:v>
       </x:c>
-      <x:c r="M4" s="89" t="str">
+      <x:c r="Q4" s="89" t="str">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="N4" s="44" t="str">
+      <x:c r="R4" s="44" t="str">
         <x:v>第一波优先触达。用“中腰部移动游戏集团需要可运营项目”作为开场逻辑。</x:v>
       </x:c>
-      <x:c r="O4" s="44" t="str">
+      <x:c r="S4" s="44" t="str">
         <x:v>https://www.eastsidegamesgroup.com/</x:v>
       </x:c>
-      <x:c r="P4" s="44" t="str">
+      <x:c r="T4" s="44" t="str">
         <x:v>https://www.eastsidegamesgroup.com/games/</x:v>
       </x:c>
-      <x:c r="Q4" s="45" t="str">
+      <x:c r="U4" s="44" t="str">
         <x:v>https://investors.eastsidegamesgroup.com/</x:v>
+      </x:c>
+      <x:c r="V4" s="45" t="str">
+        <x:v>https://eastsidegamesgroup.com/contact/</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="60" hidden="0" customHeight="1">
@@ -966,37 +1031,52 @@
         <x:v>https://lionstudios.cc/</x:v>
       </x:c>
       <x:c r="G5" s="44" t="str">
+        <x:v>Lion Studios 官网披露已发布 140+ games，25+ games reached #1；Tripledot 2025 收购 AppLovin games business 后获得多个美国移动游戏资产。</x:v>
+      </x:c>
+      <x:c r="H5" s="44" t="str">
+        <x:v>Love Balls, Mr Bullet, Happy Glass, Match 3D, Hexa Sort, Wordscapes/PeopleFun, Project Makeover/Magic Tavern</x:v>
+      </x:c>
+      <x:c r="I5" s="44" t="str">
+        <x:v>hello@lionstudios.cc; support@lionstudios.cc</x:v>
+      </x:c>
+      <x:c r="J5" s="44" t="str">
+        <x:v>Google Play 开发者页公开 hello@；官网主要使用 contact/publishing submission form。</x:v>
+      </x:c>
+      <x:c r="K5" s="44" t="str">
         <x:v>益世界式移动发行/买量体系</x:v>
       </x:c>
-      <x:c r="H5" s="44" t="str">
+      <x:c r="L5" s="44" t="str">
         <x:v>Lion Studios 是北美移动发行和买量体系的重要玩家；Tripledot 2025 年收购 AppLovin 游戏业务后，组合里包含 Lion Studios、Machine Zone、PeopleFun、Magic Tavern 等美国资产。</x:v>
       </x:c>
-      <x:c r="I5" s="44" t="str">
+      <x:c r="M5" s="44" t="str">
         <x:v>适合谈移动休闲/混合休闲发行、买量扩张、项目收购或把团队并入更大的移动发行体系。</x:v>
       </x:c>
-      <x:c r="J5" s="44" t="str">
+      <x:c r="N5" s="44" t="str">
         <x:v>发行；UA/增长；项目收购；团队收购</x:v>
       </x:c>
-      <x:c r="K5" s="44" t="str">
+      <x:c r="O5" s="44" t="str">
         <x:v>Lion Studios publishing / Tripledot corporate development</x:v>
       </x:c>
-      <x:c r="L5" s="44" t="str">
+      <x:c r="P5" s="44" t="str">
         <x:v>Lion Studios submission / Tripledot contact / LinkedIn</x:v>
       </x:c>
-      <x:c r="M5" s="89" t="str">
+      <x:c r="Q5" s="89" t="str">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="N5" s="44" t="str">
+      <x:c r="R5" s="44" t="str">
         <x:v>第一波优先触达。注意总部不完全在北美，但北美发行与工作室资产高度相关。</x:v>
       </x:c>
-      <x:c r="O5" s="44" t="str">
+      <x:c r="S5" s="44" t="str">
         <x:v>https://lionstudios.cc/</x:v>
       </x:c>
-      <x:c r="P5" s="44" t="str">
+      <x:c r="T5" s="44" t="str">
         <x:v>https://www.applovin.com/blog/applovin-sells-apps-business-to-tripledot-studios/</x:v>
       </x:c>
-      <x:c r="Q5" s="45" t="str">
+      <x:c r="U5" s="44" t="str">
         <x:v>https://www.businesswire.com/news/home/20250219750135/en/Tripledot-Studios-to-Acquire-AppLovins-Games-Business</x:v>
+      </x:c>
+      <x:c r="V5" s="45" t="str">
+        <x:v>https://lionstudios.cc/contact-us/</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="36" hidden="0" customHeight="1">
@@ -1019,38 +1099,51 @@
         <x:v>https://griffingp.com/</x:v>
       </x:c>
       <x:c r="G6" s="44" t="str">
+        <x:v>官网披露 $1.5B under management；游戏专项 VC，投 seed 到 pre-IPO。</x:v>
+      </x:c>
+      <x:c r="H6" s="44" t="str">
+        <x:v>投资/组合：Discord, AppLovin, Scopely, Second Dinner/Marvel Snap, Overwolf, Tactile, Spyke Games</x:v>
+      </x:c>
+      <x:c r="I6" s="44" t="str">
+        <x:v>contact@griffingp.com</x:v>
+      </x:c>
+      <x:c r="J6" s="44" t="str">
+        <x:v>官网底部公开 contact@；也有 Submit Your Game 入口。</x:v>
+      </x:c>
+      <x:c r="K6" s="44" t="str">
         <x:v>纯游戏投资机构</x:v>
       </x:c>
-      <x:c r="H6" s="44" t="str">
+      <x:c r="L6" s="44" t="str">
         <x:v>北美最重要的游戏专项投资机构之一，适合在没有现金流但数据验证不错时作为财务投资/战略融资入口。</x:v>
       </x:c>
-      <x:c r="I6" s="44" t="str">
+      <x:c r="M6" s="44" t="str">
         <x:v>不负责发行，但可能投资团队、帮助接触发行商或参与并购/融资结构设计。</x:v>
       </x:c>
-      <x:c r="J6" s="44" t="str">
+      <x:c r="N6" s="44" t="str">
         <x:v>股权投资；桥接融资；战略投资转介；并购介绍</x:v>
       </x:c>
-      <x:c r="K6" s="44" t="str">
+      <x:c r="O6" s="44" t="str">
         <x:v>Investment team / partner network</x:v>
       </x:c>
-      <x:c r="L6" s="44" t="str">
+      <x:c r="P6" s="44" t="str">
         <x:v>官网 contact / partner LinkedIn / portfolio warm intro</x:v>
       </x:c>
-      <x:c r="M6" s="89" t="str">
+      <x:c r="Q6" s="89" t="str">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="N6" s="44" t="str">
+      <x:c r="R6" s="44" t="str">
         <x:v>与发行商并行触达，邮件要更像融资 teaser：团队、验证数据、资金缺口、里程碑和交易结构。</x:v>
       </x:c>
-      <x:c r="O6" s="44" t="str">
+      <x:c r="S6" s="44" t="str">
         <x:v>https://griffingp.com/</x:v>
       </x:c>
-      <x:c r="P6" s="44" t="str">
+      <x:c r="T6" s="44" t="str">
         <x:v>https://griffingp.com/portfolio/</x:v>
       </x:c>
-      <x:c r="Q6" s="45" t="str">
+      <x:c r="U6" s="44" t="str">
         <x:v>https://www.gamesindustry.biz/griffin-gaming-partners-raises-750m-for-second-gaming-fund</x:v>
       </x:c>
+      <x:c r="V6" s="45" t="str"/>
     </x:row>
     <x:row r="7" ht="36" hidden="0" customHeight="1">
       <x:c r="A7" s="88" t="str">
@@ -1072,40 +1165,53 @@
         <x:v>https://www.playstudios.com/</x:v>
       </x:c>
       <x:c r="G7" s="44" t="str">
+        <x:v>纳斯达克上市公司；FY2025 revenue 约 $235.1M；playAWARDS 覆盖 17 个国家和四大洲合作伙伴。</x:v>
+      </x:c>
+      <x:c r="H7" s="44" t="str">
+        <x:v>myVEGAS Slots, myVEGAS Bingo, MGM Slots Live, Tetris mobile, POP! Slots, Solitaire/Brainium portfolio</x:v>
+      </x:c>
+      <x:c r="I7" s="44" t="str">
+        <x:v>IR@playstudios.com; media@playstudios.com</x:v>
+      </x:c>
+      <x:c r="J7" s="44" t="str">
+        <x:v>IR 官网公开 IR@；SEC/新闻稿资料公开 media@。</x:v>
+      </x:c>
+      <x:c r="K7" s="44" t="str">
         <x:v>移动休闲/社交游戏上市公司</x:v>
       </x:c>
-      <x:c r="H7" s="44" t="str">
+      <x:c r="L7" s="44" t="str">
         <x:v>美国上市移动游戏公司，规模不如 Zynga/Scopely，但在休闲、社交娱乐场景和并购上具备实操能力。</x:v>
       </x:c>
-      <x:c r="I7" s="44" t="str">
+      <x:c r="M7" s="44" t="str">
         <x:v>Family Island 类项目不是其最核心品类，但美国测试数据、休闲用户和长期活动运营可形成可评估机会。</x:v>
       </x:c>
-      <x:c r="J7" s="44" t="str">
+      <x:c r="N7" s="44" t="str">
         <x:v>战略投资；收购；发行/运营合作；IP/品牌合作</x:v>
       </x:c>
-      <x:c r="K7" s="44" t="str">
+      <x:c r="O7" s="44" t="str">
         <x:v>Corporate Development / Investor Relations / Business Development</x:v>
       </x:c>
-      <x:c r="L7" s="44" t="str">
+      <x:c r="P7" s="44" t="str">
         <x:v>官网 contact / IR contact / LinkedIn</x:v>
       </x:c>
-      <x:c r="M7" s="89" t="str">
+      <x:c r="Q7" s="89" t="str">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="N7" s="44" t="str">
+      <x:c r="R7" s="44" t="str">
         <x:v>第一波末或第二波开头触达。强调移动休闲、美国用户验证和可选交易结构。</x:v>
       </x:c>
-      <x:c r="O7" s="44" t="str">
+      <x:c r="S7" s="44" t="str">
         <x:v>https://www.playstudios.com/</x:v>
       </x:c>
-      <x:c r="P7" s="44" t="str">
+      <x:c r="T7" s="44" t="str">
         <x:v>https://ir.playstudios.com/</x:v>
       </x:c>
-      <x:c r="Q7" s="45" t="str">
+      <x:c r="U7" s="44" t="str">
         <x:v>https://www.playstudios.com/games/</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" ht="24" hidden="0" customHeight="1">
+      <x:c r="V7" s="45" t="str"/>
+    </x:row>
+    <x:row r="8" ht="36" hidden="0" customHeight="1">
       <x:c r="A8" s="88" t="str">
         <x:v>7</x:v>
       </x:c>
@@ -1125,40 +1231,55 @@
         <x:v>https://hyperbeard.com/</x:v>
       </x:c>
       <x:c r="G8" s="44" t="str">
+        <x:v>墨西哥休闲移动游戏公司；公开资料常见为约 51-200 人级，全球休闲/cute portfolio。</x:v>
+      </x:c>
+      <x:c r="H8" s="44" t="str">
+        <x:v>Adorable Home, Tsuki's Odyssey, KleptoCats, Pocket Love, My Dear Farm, Kuma Sushi Bar</x:v>
+      </x:c>
+      <x:c r="I8" s="44" t="str">
+        <x:v>publishing@hyperbeard.com; hola@hyperbeard.com; help@hyperbeard.com</x:v>
+      </x:c>
+      <x:c r="J8" s="44" t="str">
+        <x:v>官网 Contact 页公开 Publishing/Contact/Help 邮箱；发行合作优先 publishing@。</x:v>
+      </x:c>
+      <x:c r="K8" s="44" t="str">
         <x:v>北美中腰部休闲移动发行/开发商</x:v>
       </x:c>
-      <x:c r="H8" s="44" t="str">
+      <x:c r="L8" s="44" t="str">
         <x:v>墨西哥移动游戏公司，强在可爱风格、休闲移动游戏和全球发行；虽不是美国公司，但属于北美且与休闲品类贴近。</x:v>
       </x:c>
-      <x:c r="I8" s="44" t="str">
+      <x:c r="M8" s="44" t="str">
         <x:v>如果项目美术和用户情绪更偏 cozy/cute，HyperBeard 的受众和发行审美可能有匹配。</x:v>
       </x:c>
-      <x:c r="J8" s="44" t="str">
+      <x:c r="N8" s="44" t="str">
         <x:v>发行；联合开发；项目合作；少数投资可能性</x:v>
       </x:c>
-      <x:c r="K8" s="44" t="str">
+      <x:c r="O8" s="44" t="str">
         <x:v>Publishing / Business Development</x:v>
       </x:c>
-      <x:c r="L8" s="44" t="str">
+      <x:c r="P8" s="44" t="str">
         <x:v>官网 contact / submissions / LinkedIn</x:v>
       </x:c>
-      <x:c r="M8" s="89" t="str">
+      <x:c r="Q8" s="89" t="str">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="N8" s="44" t="str">
+      <x:c r="R8" s="44" t="str">
         <x:v>第一波末触达。邮件里多放视觉风格、核心循环和美国测试学习。</x:v>
       </x:c>
-      <x:c r="O8" s="44" t="str">
+      <x:c r="S8" s="44" t="str">
         <x:v>https://hyperbeard.com/</x:v>
       </x:c>
-      <x:c r="P8" s="44" t="str">
+      <x:c r="T8" s="44" t="str">
         <x:v>https://hyperbeard.com/games/</x:v>
       </x:c>
-      <x:c r="Q8" s="45" t="str">
+      <x:c r="U8" s="44" t="str">
         <x:v>https://www.pocketgamer.biz/the-top-50-mobile-game-makers-of-2024/</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" ht="24" hidden="0" customHeight="1">
+      <x:c r="V8" s="45" t="str">
+        <x:v>https://hyperbeard.com/contact-us/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="36" hidden="0" customHeight="1">
       <x:c r="A9" s="88" t="str">
         <x:v>8</x:v>
       </x:c>
@@ -1178,40 +1299,55 @@
         <x:v>https://www.bitkraft.vc/</x:v>
       </x:c>
       <x:c r="G9" s="44" t="str">
+        <x:v>官网媒体资料披露 $1.05B AUM、6 funds、130+ portfolio companies。</x:v>
+      </x:c>
+      <x:c r="H9" s="44" t="str">
+        <x:v>投资/组合：Inworld, Carry1st, Frost Giant, Immutable, Anzu, Theorycraft, Resolution Games</x:v>
+      </x:c>
+      <x:c r="I9" s="44" t="str">
+        <x:v>pitch@bitkraft.vc; investor-relations@bitkraft.vc; press@bitkraft.vc</x:v>
+      </x:c>
+      <x:c r="J9" s="44" t="str">
+        <x:v>官网 Contact 页公开 pitch@ 和 investor-relations@；融资项目优先 pitch@。</x:v>
+      </x:c>
+      <x:c r="K9" s="44" t="str">
         <x:v>纯游戏投资机构</x:v>
       </x:c>
-      <x:c r="H9" s="44" t="str">
+      <x:c r="L9" s="44" t="str">
         <x:v>全球知名游戏与互动娱乐 VC，在北美有强投资触达；适合融资和买方转介。</x:v>
       </x:c>
-      <x:c r="I9" s="44" t="str">
+      <x:c r="M9" s="44" t="str">
         <x:v>不直接发行，但可评估游戏团队、产品数据和后续融资/并购路径。</x:v>
       </x:c>
-      <x:c r="J9" s="44" t="str">
+      <x:c r="N9" s="44" t="str">
         <x:v>股权投资；桥接融资；战略介绍</x:v>
       </x:c>
-      <x:c r="K9" s="44" t="str">
+      <x:c r="O9" s="44" t="str">
         <x:v>Investment team</x:v>
       </x:c>
-      <x:c r="L9" s="44" t="str">
+      <x:c r="P9" s="44" t="str">
         <x:v>官网 contact / partner LinkedIn / portfolio warm intro</x:v>
       </x:c>
-      <x:c r="M9" s="89" t="str">
+      <x:c r="Q9" s="89" t="str">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="N9" s="44" t="str">
+      <x:c r="R9" s="44" t="str">
         <x:v>作为融资并行线第一波触达，准备投资人版 KPI teaser。</x:v>
       </x:c>
-      <x:c r="O9" s="44" t="str">
+      <x:c r="S9" s="44" t="str">
         <x:v>https://www.bitkraft.vc/</x:v>
       </x:c>
-      <x:c r="P9" s="44" t="str">
+      <x:c r="T9" s="44" t="str">
         <x:v>https://www.bitkraft.vc/portfolio</x:v>
       </x:c>
-      <x:c r="Q9" s="45" t="str">
+      <x:c r="U9" s="44" t="str">
         <x:v>https://www.bitkraft.vc/team</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" ht="24" hidden="0" customHeight="1">
+      <x:c r="V9" s="45" t="str">
+        <x:v>https://www.bitkraft.vc/contact/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="36" hidden="0" customHeight="1">
       <x:c r="A10" s="88" t="str">
         <x:v>9</x:v>
       </x:c>
@@ -1231,37 +1367,52 @@
         <x:v>https://www.bigbluebubble.com/</x:v>
       </x:c>
       <x:c r="G10" s="44" t="str">
+        <x:v>官网披露 100+ titles；My Singing Monsters franchise 100M+ downloads；EG7 体系，约 75 人级公开资料。</x:v>
+      </x:c>
+      <x:c r="H10" s="44" t="str">
+        <x:v>My Singing Monsters, My Singing Monsters: Dawn of Fire, My Singing Monsters Composer, Power Chord, Foregone</x:v>
+      </x:c>
+      <x:c r="I10" s="44" t="str">
+        <x:v>contact@bigbluebubble.com; press@bigbluebubble.com</x:v>
+      </x:c>
+      <x:c r="J10" s="44" t="str">
+        <x:v>官网 business inquiries 使用 contact@；press kit 公开 press@。</x:v>
+      </x:c>
+      <x:c r="K10" s="44" t="str">
         <x:v>移动休闲开发发行商</x:v>
       </x:c>
-      <x:c r="H10" s="44" t="str">
+      <x:c r="L10" s="44" t="str">
         <x:v>加拿大老牌独立移动/休闲游戏公司，代表作 My Singing Monsters，行业地位更像中腰部精品型而非大平台。</x:v>
       </x:c>
-      <x:c r="I10" s="44" t="str">
+      <x:c r="M10" s="44" t="str">
         <x:v>对休闲模拟、收集、养成和长线内容运营有可读性；收购能力未知，但适合询问合作/发行/转介绍。</x:v>
       </x:c>
-      <x:c r="J10" s="44" t="str">
+      <x:c r="N10" s="44" t="str">
         <x:v>发行合作；联合开发；战略合作；小规模投资可能性</x:v>
       </x:c>
-      <x:c r="K10" s="44" t="str">
+      <x:c r="O10" s="44" t="str">
         <x:v>Business Development / Studio leadership</x:v>
       </x:c>
-      <x:c r="L10" s="44" t="str">
+      <x:c r="P10" s="44" t="str">
         <x:v>官网 contact / LinkedIn</x:v>
       </x:c>
-      <x:c r="M10" s="89" t="str">
+      <x:c r="Q10" s="89" t="str">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="N10" s="44" t="str">
+      <x:c r="R10" s="44" t="str">
         <x:v>第二波触达。突出玩法循环、内容产能和可持续 LiveOps。</x:v>
       </x:c>
-      <x:c r="O10" s="44" t="str">
+      <x:c r="S10" s="44" t="str">
         <x:v>https://www.bigbluebubble.com/</x:v>
       </x:c>
-      <x:c r="P10" s="44" t="str">
+      <x:c r="T10" s="44" t="str">
         <x:v>https://www.bigbluebubble.com/games/</x:v>
       </x:c>
-      <x:c r="Q10" s="45" t="str">
+      <x:c r="U10" s="44" t="str">
         <x:v>https://www.bigbluebubble.com/about/</x:v>
+      </x:c>
+      <x:c r="V10" s="45" t="str">
+        <x:v>https://www.bigbluebubble.com/home/contact/</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="36" hidden="0" customHeight="1">
@@ -1284,37 +1435,52 @@
         <x:v>https://www.mobilityware.com/</x:v>
       </x:c>
       <x:c r="G11" s="44" t="str">
+        <x:v>公开资料显示 101-250 人级；Solitaire/card/puzzle portfolio 累计 200M+ downloads。</x:v>
+      </x:c>
+      <x:c r="H11" s="44" t="str">
+        <x:v>Solitaire, Spider Solitaire, FreeCell, MONOPOLY Solitaire, Pyramid Solitaire, Hearts, Mahjong</x:v>
+      </x:c>
+      <x:c r="I11" s="44" t="str">
+        <x:v>support@mobilityware.com</x:v>
+      </x:c>
+      <x:c r="J11" s="44" t="str">
+        <x:v>公开版权/支持页列 support@；未找到公开 BD 邮箱。</x:v>
+      </x:c>
+      <x:c r="K11" s="44" t="str">
         <x:v>北美休闲移动游戏公司</x:v>
       </x:c>
-      <x:c r="H11" s="44" t="str">
+      <x:c r="L11" s="44" t="str">
         <x:v>美国休闲移动游戏老牌公司，强在 evergreen casual 与移动端运营；行业体量大概率低于 Jam City，但在休闲用户上有价值。</x:v>
       </x:c>
-      <x:c r="I11" s="44" t="str">
+      <x:c r="M11" s="44" t="str">
         <x:v>品类不完全相同，但美国休闲用户、低 CPI 和留存验证是共通语言。</x:v>
       </x:c>
-      <x:c r="J11" s="44" t="str">
+      <x:c r="N11" s="44" t="str">
         <x:v>发行合作；联合开发；项目评估；收购可能性低到中</x:v>
       </x:c>
-      <x:c r="K11" s="44" t="str">
+      <x:c r="O11" s="44" t="str">
         <x:v>Business Development / Studio leadership</x:v>
       </x:c>
-      <x:c r="L11" s="44" t="str">
+      <x:c r="P11" s="44" t="str">
         <x:v>官网 contact / LinkedIn</x:v>
       </x:c>
-      <x:c r="M11" s="89" t="str">
+      <x:c r="Q11" s="89" t="str">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N11" s="44" t="str">
+      <x:c r="R11" s="44" t="str">
         <x:v>第二波触达。邮件要简洁，不要一开始就只谈收购。</x:v>
       </x:c>
-      <x:c r="O11" s="44" t="str">
+      <x:c r="S11" s="44" t="str">
         <x:v>https://www.mobilityware.com/</x:v>
       </x:c>
-      <x:c r="P11" s="44" t="str">
+      <x:c r="T11" s="44" t="str">
         <x:v>https://www.mobilityware.com/games/</x:v>
       </x:c>
-      <x:c r="Q11" s="45" t="str">
+      <x:c r="U11" s="44" t="str">
         <x:v>https://www.mobilityware.com/about-us/</x:v>
+      </x:c>
+      <x:c r="V11" s="45" t="str">
+        <x:v>https://www.mobilityware.com/copyright/</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="36" hidden="0" customHeight="1">
@@ -1337,40 +1503,55 @@
         <x:v>https://www.bigfishgames.com/</x:v>
       </x:c>
       <x:c r="G12" s="44" t="str">
+        <x:v>老牌休闲游戏公司；公开资料显示约 350 人级；历史累计 1B+ game downloads。</x:v>
+      </x:c>
+      <x:c r="H12" s="44" t="str">
+        <x:v>EverMerge, Gummy Drop!, Fairway Solitaire, Mystery Case Files, Midnight Castle, Cooking Craze</x:v>
+      </x:c>
+      <x:c r="I12" s="44" t="str">
+        <x:v>premiumsubmissions@bigfishgames.com; support via Zendesk form</x:v>
+      </x:c>
+      <x:c r="J12" s="44" t="str">
+        <x:v>公开资料可见 submissions 邮箱；官网支持主要走 Zendesk 表单，当前商务状态需先确认。</x:v>
+      </x:c>
+      <x:c r="K12" s="44" t="str">
         <x:v>休闲游戏发行/分发老牌公司</x:v>
       </x:c>
-      <x:c r="H12" s="44" t="str">
+      <x:c r="L12" s="44" t="str">
         <x:v>曾是北美休闲游戏发行和分发的重要公司；当前战略状态需谨慎核验，但其休闲用户和发行历史与本项目相关。</x:v>
       </x:c>
-      <x:c r="I12" s="44" t="str">
+      <x:c r="M12" s="44" t="str">
         <x:v>Family Island 类项目可从休闲冒险、模拟经营、长期内容和女性/家庭向用户角度切入。</x:v>
       </x:c>
-      <x:c r="J12" s="44" t="str">
+      <x:c r="N12" s="44" t="str">
         <x:v>发行；分发；资产合作；收购可能性不确定</x:v>
       </x:c>
-      <x:c r="K12" s="44" t="str">
+      <x:c r="O12" s="44" t="str">
         <x:v>Business Development / publishing leadership</x:v>
       </x:c>
-      <x:c r="L12" s="44" t="str">
+      <x:c r="P12" s="44" t="str">
         <x:v>官网 support/contact / LinkedIn / 前员工或集团转介绍</x:v>
       </x:c>
-      <x:c r="M12" s="89" t="str">
+      <x:c r="Q12" s="89" t="str">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="N12" s="44" t="str">
+      <x:c r="R12" s="44" t="str">
         <x:v>第二波触达。先确认当前是否仍评估外部移动项目。</x:v>
       </x:c>
-      <x:c r="O12" s="44" t="str">
+      <x:c r="S12" s="44" t="str">
         <x:v>https://www.bigfishgames.com/us/en/company.html</x:v>
       </x:c>
-      <x:c r="P12" s="44" t="str">
+      <x:c r="T12" s="44" t="str">
         <x:v>https://www.bigfishgames.com/us/en/games.html</x:v>
       </x:c>
-      <x:c r="Q12" s="45" t="str">
+      <x:c r="U12" s="44" t="str">
         <x:v>https://www.gamesindustry.biz/aristocrat-sells-big-fish-games-to-bfg-entertainment</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="24" hidden="0" customHeight="1">
+      <x:c r="V12" s="45" t="str">
+        <x:v>https://bigfishgames.zendesk.com/hc/en-us/sections/115000328528-Contact-Us</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="36" hidden="0" customHeight="1">
       <x:c r="A13" s="88" t="str">
         <x:v>12</x:v>
       </x:c>
@@ -1390,38 +1571,51 @@
         <x:v>https://makersfund.com/</x:v>
       </x:c>
       <x:c r="G13" s="44" t="str">
+        <x:v>全球 games/interactive entertainment VC；公开 portfolio 覆盖 Dream Games, TrailMix, Theorycraft 等。</x:v>
+      </x:c>
+      <x:c r="H13" s="44" t="str">
+        <x:v>投资/组合：Dream Games/Royal Match, Theorycraft, TrailMix/Love &amp; Pies, FRVR, Mainframe, Mino Games</x:v>
+      </x:c>
+      <x:c r="I13" s="44" t="str">
+        <x:v>info@makersfund.com</x:v>
+      </x:c>
+      <x:c r="J13" s="44" t="str">
+        <x:v>第三方机构档案列 info@；官网主要使用 Contact Us/团队引荐。</x:v>
+      </x:c>
+      <x:c r="K13" s="44" t="str">
         <x:v>纯游戏投资机构</x:v>
       </x:c>
-      <x:c r="H13" s="44" t="str">
+      <x:c r="L13" s="44" t="str">
         <x:v>游戏和互动娱乐专项基金，适合早中期游戏公司融资和并购路径讨论。</x:v>
       </x:c>
-      <x:c r="I13" s="44" t="str">
+      <x:c r="M13" s="44" t="str">
         <x:v>可评估已验证美国测试数据的移动游戏团队，但不会替代发行商。</x:v>
       </x:c>
-      <x:c r="J13" s="44" t="str">
+      <x:c r="N13" s="44" t="str">
         <x:v>股权投资；桥接融资；战略转介</x:v>
       </x:c>
-      <x:c r="K13" s="44" t="str">
+      <x:c r="O13" s="44" t="str">
         <x:v>Investment team</x:v>
       </x:c>
-      <x:c r="L13" s="44" t="str">
+      <x:c r="P13" s="44" t="str">
         <x:v>官网 contact / partner LinkedIn / portfolio intro</x:v>
       </x:c>
-      <x:c r="M13" s="89" t="str">
+      <x:c r="Q13" s="89" t="str">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="N13" s="44" t="str">
+      <x:c r="R13" s="44" t="str">
         <x:v>第二波投资线触达。准备融资版 teaser 和 12 个月里程碑预算。</x:v>
       </x:c>
-      <x:c r="O13" s="44" t="str">
+      <x:c r="S13" s="44" t="str">
         <x:v>https://makersfund.com/</x:v>
       </x:c>
-      <x:c r="P13" s="44" t="str">
+      <x:c r="T13" s="44" t="str">
         <x:v>https://makersfund.com/portfolio/</x:v>
       </x:c>
-      <x:c r="Q13" s="45" t="str">
+      <x:c r="U13" s="44" t="str">
         <x:v>https://makersfund.com/team/</x:v>
       </x:c>
+      <x:c r="V13" s="45" t="str"/>
     </x:row>
     <x:row r="14" ht="36" hidden="0" customHeight="1">
       <x:c r="A14" s="88" t="str">
@@ -1443,38 +1637,51 @@
         <x:v>https://www.tapblaze.com/</x:v>
       </x:c>
       <x:c r="G14" s="44" t="str">
+        <x:v>洛杉矶小到中型休闲模拟工作室；Good Pizza, Great Pizza 跨 iOS/Android/Steam/Switch，多平台长线运营。</x:v>
+      </x:c>
+      <x:c r="H14" s="44" t="str">
+        <x:v>Good Pizza, Great Pizza; Good Coffee, Great Coffee; Homecraft; My Pizza Shop 系列</x:v>
+      </x:c>
+      <x:c r="I14" s="44" t="str">
+        <x:v>pizza@tapblaze.com</x:v>
+      </x:c>
+      <x:c r="J14" s="44" t="str">
+        <x:v>Good Pizza 社区/支持资料常用 pizza@；未找到公开公司 BD 邮箱。</x:v>
+      </x:c>
+      <x:c r="K14" s="44" t="str">
         <x:v>休闲模拟开发发行商</x:v>
       </x:c>
-      <x:c r="H14" s="44" t="str">
+      <x:c r="L14" s="44" t="str">
         <x:v>美国小到中型移动休闲工作室，代表作 Good Pizza, Great Pizza；不一定是买方，但品类经验非常贴近。</x:v>
       </x:c>
-      <x:c r="I14" s="44" t="str">
+      <x:c r="M14" s="44" t="str">
         <x:v>餐厅模拟和 cozy 休闲运营与 Family Island 类用户存在重合，适合谈合作、发行建议或小规模战略合作。</x:v>
       </x:c>
-      <x:c r="J14" s="44" t="str">
+      <x:c r="N14" s="44" t="str">
         <x:v>联合开发；发行建议；小规模合作；收购可能性低</x:v>
       </x:c>
-      <x:c r="K14" s="44" t="str">
+      <x:c r="O14" s="44" t="str">
         <x:v>Founder / Business Development</x:v>
       </x:c>
-      <x:c r="L14" s="44" t="str">
+      <x:c r="P14" s="44" t="str">
         <x:v>官网 contact / LinkedIn</x:v>
       </x:c>
-      <x:c r="M14" s="89" t="str">
+      <x:c r="Q14" s="89" t="str">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="N14" s="44" t="str">
+      <x:c r="R14" s="44" t="str">
         <x:v>第二波触达。更像合作伙伴或行业转介绍，不要把收购诉求放得太重。</x:v>
       </x:c>
-      <x:c r="O14" s="44" t="str">
+      <x:c r="S14" s="44" t="str">
         <x:v>https://www.tapblaze.com/</x:v>
       </x:c>
-      <x:c r="P14" s="44" t="str">
+      <x:c r="T14" s="44" t="str">
         <x:v>https://www.tapblaze.com/games/</x:v>
       </x:c>
-      <x:c r="Q14" s="45" t="str">
+      <x:c r="U14" s="44" t="str">
         <x:v>https://play.google.com/store/apps/dev?id=5416792938617747564</x:v>
       </x:c>
+      <x:c r="V14" s="45" t="str"/>
     </x:row>
     <x:row r="15" ht="36" hidden="0" customHeight="1">
       <x:c r="A15" s="88" t="str">
@@ -1496,40 +1703,55 @@
         <x:v>https://www.konvoy.vc/</x:v>
       </x:c>
       <x:c r="G15" s="44" t="str">
+        <x:v>美国游戏专项 VC；公开基金信息显示 Fund III $150M，游戏/平台/基础设施投资网络。</x:v>
+      </x:c>
+      <x:c r="H15" s="44" t="str">
+        <x:v>投资/组合：Axie Infinity/Sky Mavis, Ready Player Me, Genopets, Carry1st, Metafy, Windwalk</x:v>
+      </x:c>
+      <x:c r="I15" s="44" t="str">
+        <x:v>未找到公开通用投资邮箱；使用官网 contact/newsletter form 和合伙人 LinkedIn</x:v>
+      </x:c>
+      <x:c r="J15" s="44" t="str">
+        <x:v>官网 About/Contact 以表单和团队页为主；建议走 warm intro。</x:v>
+      </x:c>
+      <x:c r="K15" s="44" t="str">
         <x:v>纯游戏投资机构</x:v>
       </x:c>
-      <x:c r="H15" s="44" t="str">
+      <x:c r="L15" s="44" t="str">
         <x:v>美国游戏专项 VC，关注游戏、平台和相关技术，适合作为融资与买方网络入口。</x:v>
       </x:c>
-      <x:c r="I15" s="44" t="str">
+      <x:c r="M15" s="44" t="str">
         <x:v>对产品 KPI、团队效率和市场验证敏感，能帮助判断项目是否达到融资门槛。</x:v>
       </x:c>
-      <x:c r="J15" s="44" t="str">
+      <x:c r="N15" s="44" t="str">
         <x:v>股权投资；桥接融资；买方/发行商介绍</x:v>
       </x:c>
-      <x:c r="K15" s="44" t="str">
+      <x:c r="O15" s="44" t="str">
         <x:v>Investment team</x:v>
       </x:c>
-      <x:c r="L15" s="44" t="str">
+      <x:c r="P15" s="44" t="str">
         <x:v>官网 contact / partner LinkedIn</x:v>
       </x:c>
-      <x:c r="M15" s="89" t="str">
+      <x:c r="Q15" s="89" t="str">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="N15" s="44" t="str">
+      <x:c r="R15" s="44" t="str">
         <x:v>第二波投资线触达。把现金流缺口表述为明确 runway 与里程碑，而不是危机叙事。</x:v>
       </x:c>
-      <x:c r="O15" s="44" t="str">
+      <x:c r="S15" s="44" t="str">
         <x:v>https://www.konvoy.vc/</x:v>
       </x:c>
-      <x:c r="P15" s="44" t="str">
+      <x:c r="T15" s="44" t="str">
         <x:v>https://www.konvoy.vc/portfolio</x:v>
       </x:c>
-      <x:c r="Q15" s="45" t="str">
+      <x:c r="U15" s="44" t="str">
         <x:v>https://www.konvoy.vc/team</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" ht="24" hidden="0" customHeight="1">
+      <x:c r="V15" s="45" t="str">
+        <x:v>https://www.konvoy.vc/about</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="36" hidden="0" customHeight="1">
       <x:c r="A16" s="88" t="str">
         <x:v>15</x:v>
       </x:c>
@@ -1549,40 +1771,55 @@
         <x:v>https://www.storm8.com/</x:v>
       </x:c>
       <x:c r="G16" s="44" t="str">
+        <x:v>Storm8 为 Stillfront 旗下美国移动游戏工作室；历史累计 1B+ downloads 级别公开说法。</x:v>
+      </x:c>
+      <x:c r="H16" s="44" t="str">
+        <x:v>Restaurant Story, Dragon Story, Property Brothers Home Design, Home Design Makeover, Castle Story, Bubble Mania</x:v>
+      </x:c>
+      <x:c r="I16" s="44" t="str">
+        <x:v>publishing@storm8.com; businessdevelopment@storm8.com; ua@storm8.com; pr@storm8.com</x:v>
+      </x:c>
+      <x:c r="J16" s="44" t="str">
+        <x:v>Storm8 官网 Contact 页公开 Publishing/BD/UA/PR 邮箱。</x:v>
+      </x:c>
+      <x:c r="K16" s="44" t="str">
         <x:v>移动休闲/社交游戏工作室</x:v>
       </x:c>
-      <x:c r="H16" s="44" t="str">
+      <x:c r="L16" s="44" t="str">
         <x:v>美国移动游戏老牌工作室，现属 Stillfront；曾在休闲、社交和女性向移动用户上有较强经验。</x:v>
       </x:c>
-      <x:c r="I16" s="44" t="str">
+      <x:c r="M16" s="44" t="str">
         <x:v>品类和用户画像有相关性，但决策链可能在母集团，外部收购/发行意愿需确认。</x:v>
       </x:c>
-      <x:c r="J16" s="44" t="str">
+      <x:c r="N16" s="44" t="str">
         <x:v>发行/运营合作；资产收购；集团层面投资/并购</x:v>
       </x:c>
-      <x:c r="K16" s="44" t="str">
+      <x:c r="O16" s="44" t="str">
         <x:v>Storm8 leadership / Stillfront M&amp;A</x:v>
       </x:c>
-      <x:c r="L16" s="44" t="str">
+      <x:c r="P16" s="44" t="str">
         <x:v>官网 contact / Stillfront corporate contact / LinkedIn</x:v>
       </x:c>
-      <x:c r="M16" s="89" t="str">
+      <x:c r="Q16" s="89" t="str">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="N16" s="44" t="str">
+      <x:c r="R16" s="44" t="str">
         <x:v>第二波触达，同时抄送或并行找 Stillfront 投资并购入口。</x:v>
       </x:c>
-      <x:c r="O16" s="44" t="str">
+      <x:c r="S16" s="44" t="str">
         <x:v>https://www.storm8.com/</x:v>
       </x:c>
-      <x:c r="P16" s="44" t="str">
+      <x:c r="T16" s="44" t="str">
         <x:v>https://www.storm8.com/games/</x:v>
       </x:c>
-      <x:c r="Q16" s="45" t="str">
+      <x:c r="U16" s="44" t="str">
         <x:v>https://www.stillfront.com/en/portfolio/storm8/</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" ht="24" hidden="0" customHeight="1">
+      <x:c r="V16" s="45" t="str">
+        <x:v>https://www.storm8.com/contact/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="48" hidden="0" customHeight="1">
       <x:c r="A17" s="88" t="str">
         <x:v>16</x:v>
       </x:c>
@@ -1602,40 +1839,55 @@
         <x:v>https://www.kabam.com/</x:v>
       </x:c>
       <x:c r="G17" s="44" t="str">
+        <x:v>Netmarble 旗下北美 F2P 工作室；Marvel Contest of Champions 为十亿美元级长线产品。</x:v>
+      </x:c>
+      <x:c r="H17" s="44" t="str">
+        <x:v>Marvel Contest of Champions, Shop Titans, King Arthur: Legends Rise, Disney Mirrorverse, Transformers: Forged to Fight</x:v>
+      </x:c>
+      <x:c r="I17" s="44" t="str">
+        <x:v>press@kabam.com; media@kabam.com; contact@kabam.com</x:v>
+      </x:c>
+      <x:c r="J17" s="44" t="str">
+        <x:v>官网有 Contact Press/Support 入口；公开资料列 press/media/contact，商务建议 LinkedIn/Netmarble 路径并行。</x:v>
+      </x:c>
+      <x:c r="K17" s="44" t="str">
         <x:v>移动 F2P 研运发行公司</x:v>
       </x:c>
-      <x:c r="H17" s="44" t="str">
+      <x:c r="L17" s="44" t="str">
         <x:v>北美移动 F2P 和 IP 改编强公司，产品集中在中重度和授权 IP，行业地位高于一般中腰部发行商。</x:v>
       </x:c>
-      <x:c r="I17" s="44" t="str">
+      <x:c r="M17" s="44" t="str">
         <x:v>玩法不完全贴合，但其 F2P 长线运营、IP、买量和集团资源值得作为战略买方备选。</x:v>
       </x:c>
-      <x:c r="J17" s="44" t="str">
+      <x:c r="N17" s="44" t="str">
         <x:v>战略合作；项目/团队收购；发行可能性中低</x:v>
       </x:c>
-      <x:c r="K17" s="44" t="str">
+      <x:c r="O17" s="44" t="str">
         <x:v>Business Development / Studio leadership / Netmarble group route</x:v>
       </x:c>
-      <x:c r="L17" s="44" t="str">
+      <x:c r="P17" s="44" t="str">
         <x:v>官网 contact / LinkedIn / Netmarble 转介绍</x:v>
       </x:c>
-      <x:c r="M17" s="89" t="str">
+      <x:c r="Q17" s="89" t="str">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="N17" s="44" t="str">
+      <x:c r="R17" s="44" t="str">
         <x:v>第二波或第三波触达。更强调 F2P 运营和美国测试，而不是 cozy 模拟品类。</x:v>
       </x:c>
-      <x:c r="O17" s="44" t="str">
+      <x:c r="S17" s="44" t="str">
         <x:v>https://www.kabam.com/</x:v>
       </x:c>
-      <x:c r="P17" s="44" t="str">
+      <x:c r="T17" s="44" t="str">
         <x:v>https://www.kabam.com/games/</x:v>
       </x:c>
-      <x:c r="Q17" s="45" t="str">
+      <x:c r="U17" s="44" t="str">
         <x:v>https://www.netmarble.com/en/company/about</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" ht="24" hidden="0" customHeight="1">
+      <x:c r="V17" s="45" t="str">
+        <x:v>https://kabam.com/index.php</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="36" hidden="0" customHeight="1">
       <x:c r="A18" s="88" t="str">
         <x:v>17</x:v>
       </x:c>
@@ -1655,37 +1907,52 @@
         <x:v>https://transcend.fund/</x:v>
       </x:c>
       <x:c r="G18" s="44" t="str">
+        <x:v>2020 年成立的游戏/数字娱乐早期基金；LinkedIn 显示 2-10 人；合伙人具备 70+ years operator experience。</x:v>
+      </x:c>
+      <x:c r="H18" s="44" t="str">
+        <x:v>投资/组合：Gardens, Fuse Games, Odyssey Interactive, Elodie Games, Theorycraft-related networks</x:v>
+      </x:c>
+      <x:c r="I18" s="44" t="str">
+        <x:v>pitch@transcend.fund; info@transcend.fund</x:v>
+      </x:c>
+      <x:c r="J18" s="44" t="str">
+        <x:v>Crunchbase/PEI 档案列 pitch@/info@；官网主要 Contact Us。</x:v>
+      </x:c>
+      <x:c r="K18" s="44" t="str">
         <x:v>纯游戏投资机构</x:v>
       </x:c>
-      <x:c r="H18" s="44" t="str">
+      <x:c r="L18" s="44" t="str">
         <x:v>专注游戏和数字娱乐的投资基金，适合对接早期到成长期游戏团队。</x:v>
       </x:c>
-      <x:c r="I18" s="44" t="str">
+      <x:c r="M18" s="44" t="str">
         <x:v>可作为融资和买方转介入口，尤其当发行合作短期难落地时。</x:v>
       </x:c>
-      <x:c r="J18" s="44" t="str">
+      <x:c r="N18" s="44" t="str">
         <x:v>股权投资；战略转介；桥接融资</x:v>
       </x:c>
-      <x:c r="K18" s="44" t="str">
+      <x:c r="O18" s="44" t="str">
         <x:v>Investment team</x:v>
       </x:c>
-      <x:c r="L18" s="44" t="str">
+      <x:c r="P18" s="44" t="str">
         <x:v>官网 contact / partner LinkedIn</x:v>
       </x:c>
-      <x:c r="M18" s="89" t="str">
+      <x:c r="Q18" s="89" t="str">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="N18" s="44" t="str">
+      <x:c r="R18" s="44" t="str">
         <x:v>第二波投资线触达。强调美国市场测试、低成本验证和资金用途。</x:v>
       </x:c>
-      <x:c r="O18" s="44" t="str">
+      <x:c r="S18" s="44" t="str">
         <x:v>https://transcend.fund/</x:v>
       </x:c>
-      <x:c r="P18" s="44" t="str">
+      <x:c r="T18" s="44" t="str">
         <x:v>https://transcend.fund/portfolio/</x:v>
       </x:c>
-      <x:c r="Q18" s="45" t="str">
+      <x:c r="U18" s="44" t="str">
         <x:v>https://transcend.fund/team/</x:v>
+      </x:c>
+      <x:c r="V18" s="45" t="str">
+        <x:v>https://www.transcend.fund/</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="36" hidden="0" customHeight="1">
@@ -1708,37 +1975,52 @@
         <x:v>https://www.fortisgames.com/</x:v>
       </x:c>
       <x:c r="G19" s="44" t="str">
+        <x:v>Savvy Games Group 旗下全球游戏工作室网络；公开招聘/销售资料显示约 251-500 人级。</x:v>
+      </x:c>
+      <x:c r="H19" s="44" t="str">
+        <x:v>暂无已大规模发布旗舰产品；团队来自 Zynga/WB/EA 等，主打 original social games pipeline。</x:v>
+      </x:c>
+      <x:c r="I19" s="44" t="str">
+        <x:v>未找到公开通用邮箱；使用 Fortis/Savvy 官网 contact form 和 LinkedIn</x:v>
+      </x:c>
+      <x:c r="J19" s="44" t="str">
+        <x:v>官网未公开具体邮箱；集团层面可走 Savvy Contact form。</x:v>
+      </x:c>
+      <x:c r="K19" s="44" t="str">
         <x:v>新兴全球游戏集团/工作室网络</x:v>
       </x:c>
-      <x:c r="H19" s="44" t="str">
+      <x:c r="L19" s="44" t="str">
         <x:v>Savvy Games Group 旗下全球工作室网络，北美有重心，资金背景强，但不是传统第三方移动发行商。</x:v>
       </x:c>
-      <x:c r="I19" s="44" t="str">
+      <x:c r="M19" s="44" t="str">
         <x:v>适合尝试团队并入、联合开发或项目收购讨论；是否接受外部项目需要确认。</x:v>
       </x:c>
-      <x:c r="J19" s="44" t="str">
+      <x:c r="N19" s="44" t="str">
         <x:v>团队收购；联合开发；项目合作；战略投资可能性</x:v>
       </x:c>
-      <x:c r="K19" s="44" t="str">
+      <x:c r="O19" s="44" t="str">
         <x:v>Studio leadership / corporate leadership</x:v>
       </x:c>
-      <x:c r="L19" s="44" t="str">
+      <x:c r="P19" s="44" t="str">
         <x:v>官网 contact / LinkedIn / Savvy network intro</x:v>
       </x:c>
-      <x:c r="M19" s="89" t="str">
+      <x:c r="Q19" s="89" t="str">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="N19" s="44" t="str">
+      <x:c r="R19" s="44" t="str">
         <x:v>第二波末触达。重点问是否评估外部移动项目或团队并入机会。</x:v>
       </x:c>
-      <x:c r="O19" s="44" t="str">
+      <x:c r="S19" s="44" t="str">
         <x:v>https://www.fortisgames.com/</x:v>
       </x:c>
-      <x:c r="P19" s="44" t="str">
+      <x:c r="T19" s="44" t="str">
         <x:v>https://www.savvygames.com/en/our-companies/fortis/</x:v>
       </x:c>
-      <x:c r="Q19" s="45" t="str">
+      <x:c r="U19" s="44" t="str">
         <x:v>https://www.gamesindustry.biz/fortis-appoints-jeremy-gorman-as-ceo</x:v>
+      </x:c>
+      <x:c r="V19" s="45" t="str">
+        <x:v>https://www.savvygames.com/contact/</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="36" hidden="0" customHeight="1">
@@ -1761,37 +2043,52 @@
         <x:v>https://a16z.com/games/</x:v>
       </x:c>
       <x:c r="G20" s="44" t="str">
+        <x:v>a16z Games Fund One 为 $600M 专项游戏基金；a16z 总体为大型多阶段 VC 平台。</x:v>
+      </x:c>
+      <x:c r="H20" s="44" t="str">
+        <x:v>投资/组合：Roblox, Discord, Sky Mavis, Singularity 6, Mainframe, Voldex, Voldex-like UGC/games deals</x:v>
+      </x:c>
+      <x:c r="I20" s="44" t="str">
+        <x:v>未找到公开 games 专项收件邮箱；使用 Speedrun/application form、官网团队 LinkedIn 或 warm intro</x:v>
+      </x:c>
+      <x:c r="J20" s="44" t="str">
+        <x:v>a16z Games 公开鼓励 builders 联系，但未列通用邮箱；不要猜测个人邮箱。</x:v>
+      </x:c>
+      <x:c r="K20" s="44" t="str">
         <x:v>大型 VC 游戏基金</x:v>
       </x:c>
-      <x:c r="H20" s="44" t="str">
+      <x:c r="L20" s="44" t="str">
         <x:v>美国顶级 VC 的游戏专项平台，投资能力强，但对项目门槛和增长故事要求高。</x:v>
       </x:c>
-      <x:c r="I20" s="44" t="str">
+      <x:c r="M20" s="44" t="str">
         <x:v>如果 CPI/留存达到可融资阈值，可作为投资线高质量但高门槛对象。</x:v>
       </x:c>
-      <x:c r="J20" s="44" t="str">
+      <x:c r="N20" s="44" t="str">
         <x:v>股权投资；战略转介</x:v>
       </x:c>
-      <x:c r="K20" s="44" t="str">
+      <x:c r="O20" s="44" t="str">
         <x:v>Games investment team</x:v>
       </x:c>
-      <x:c r="L20" s="44" t="str">
+      <x:c r="P20" s="44" t="str">
         <x:v>官网 / partner LinkedIn / portfolio warm intro</x:v>
       </x:c>
-      <x:c r="M20" s="89" t="str">
+      <x:c r="Q20" s="89" t="str">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="N20" s="44" t="str">
+      <x:c r="R20" s="44" t="str">
         <x:v>第二波投资线触达。需要更强的市场规模、团队叙事和数据可信度。</x:v>
       </x:c>
-      <x:c r="O20" s="44" t="str">
+      <x:c r="S20" s="44" t="str">
         <x:v>https://a16z.com/games/</x:v>
       </x:c>
-      <x:c r="P20" s="44" t="str">
+      <x:c r="T20" s="44" t="str">
         <x:v>https://a16z.com/introducing-games-fund-one/</x:v>
       </x:c>
-      <x:c r="Q20" s="45" t="str">
+      <x:c r="U20" s="44" t="str">
         <x:v>https://a16z.com/portfolio/</x:v>
+      </x:c>
+      <x:c r="V20" s="45" t="str">
+        <x:v>https://a16z.com/games-fund-one-building-the-future-of-games/</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="36" hidden="0" customHeight="1">
@@ -1814,37 +2111,52 @@
         <x:v>https://www.applovin.com/</x:v>
       </x:c>
       <x:c r="G21" s="44" t="str">
+        <x:v>纳斯达克上市广告技术公司；2025 年出售 apps/games business 给 Tripledot 后核心为 Axon/广告平台。</x:v>
+      </x:c>
+      <x:c r="H21" s="44" t="str">
+        <x:v>AppDiscovery, MAX, Adjust, Wurl, Axon；原游戏资产包括 Lion Studios、Machine Zone、PeopleFun、Magic Tavern</x:v>
+      </x:c>
+      <x:c r="I21" s="44" t="str">
+        <x:v>info@applovin.com; sales@applovin.com; press@applovin.com; ir@applovin.com</x:v>
+      </x:c>
+      <x:c r="J21" s="44" t="str">
+        <x:v>官网 Contact/IR 页公开 general/sales/press/IR 邮箱。</x:v>
+      </x:c>
+      <x:c r="K21" s="44" t="str">
         <x:v>广告技术/发行生态入口</x:v>
       </x:c>
-      <x:c r="H21" s="44" t="str">
+      <x:c r="L21" s="44" t="str">
         <x:v>已经不应被当作传统游戏发行商：2025 年出售游戏业务给 Tripledot 后，核心是广告技术和平台，但仍可能通过 Tripledot 股权与生态转介产生价值。</x:v>
       </x:c>
-      <x:c r="I21" s="44" t="str">
+      <x:c r="M21" s="44" t="str">
         <x:v>不是首选买方；更适合作为 UA、发行商转介或间接触达 Lion/Tripledot 的生态入口。</x:v>
       </x:c>
-      <x:c r="J21" s="44" t="str">
+      <x:c r="N21" s="44" t="str">
         <x:v>UA/增长合作；生态转介；间接投资/收购路径</x:v>
       </x:c>
-      <x:c r="K21" s="44" t="str">
+      <x:c r="O21" s="44" t="str">
         <x:v>Business Development / AppLovin ecosystem contacts</x:v>
       </x:c>
-      <x:c r="L21" s="44" t="str">
+      <x:c r="P21" s="44" t="str">
         <x:v>官网 contact / LinkedIn / Tripledot route</x:v>
       </x:c>
-      <x:c r="M21" s="89" t="str">
+      <x:c r="Q21" s="89" t="str">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="N21" s="44" t="str">
+      <x:c r="R21" s="44" t="str">
         <x:v>不作为纯发行买方优先触达；如有 AppLovin 关系，可请其转给 Tripledot/Lion。</x:v>
       </x:c>
-      <x:c r="O21" s="44" t="str">
+      <x:c r="S21" s="44" t="str">
         <x:v>https://www.applovin.com/</x:v>
       </x:c>
-      <x:c r="P21" s="44" t="str">
+      <x:c r="T21" s="44" t="str">
         <x:v>https://www.applovin.com/blog/applovin-sells-apps-business-to-tripledot-studios/</x:v>
       </x:c>
-      <x:c r="Q21" s="45" t="str">
+      <x:c r="U21" s="44" t="str">
         <x:v>https://investors.applovin.com/</x:v>
+      </x:c>
+      <x:c r="V21" s="45" t="str">
+        <x:v>https://blog.applovin.com/contact/</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="60" hidden="0" customHeight="1">
@@ -1867,40 +2179,55 @@
         <x:v>https://www.scopely.com/</x:v>
       </x:c>
       <x:c r="G22" s="44" t="str">
+        <x:v>2023 年 Savvy 以 $4.9B 收购；2025 收购 Niantic games business；美国移动游戏头部。</x:v>
+      </x:c>
+      <x:c r="H22" s="44" t="str">
+        <x:v>MONOPOLY GO!, Star Trek Fleet Command, MARVEL Strike Force, Stumble Guys, Yahtzee with Buddies, Pokémon GO/Niantic games business</x:v>
+      </x:c>
+      <x:c r="I22" s="44" t="str">
+        <x:v>未找到公开商务邮箱；使用官网 Contact 选择 Developer Partners</x:v>
+      </x:c>
+      <x:c r="J22" s="44" t="str">
+        <x:v>官网 Contact 表单支持 Developer Partners；未公开通用 BD 邮箱。</x:v>
+      </x:c>
+      <x:c r="K22" s="44" t="str">
         <x:v>战略上限参照</x:v>
       </x:c>
-      <x:c r="H22" s="44" t="str">
+      <x:c r="L22" s="44" t="str">
         <x:v>北美移动游戏绝对强势公司之一，地位明显高于三七互娱/益世界的类比层级；作为买方可试，但不应作为主要对标。</x:v>
       </x:c>
-      <x:c r="I22" s="44" t="str">
+      <x:c r="M22" s="44" t="str">
         <x:v>如果数据非常强，休闲冒险/模拟可作为其移动 F2P portfolio 延展；否则冷启动触达难度高。</x:v>
       </x:c>
-      <x:c r="J22" s="44" t="str">
+      <x:c r="N22" s="44" t="str">
         <x:v>收购；战略投资；发行/合作可能性低</x:v>
       </x:c>
-      <x:c r="K22" s="44" t="str">
+      <x:c r="O22" s="44" t="str">
         <x:v>Corporate Development / studio leadership</x:v>
       </x:c>
-      <x:c r="L22" s="44" t="str">
+      <x:c r="P22" s="44" t="str">
         <x:v>官网 / LinkedIn / 投资并购转介绍</x:v>
       </x:c>
-      <x:c r="M22" s="89" t="str">
+      <x:c r="Q22" s="89" t="str">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="N22" s="44" t="str">
+      <x:c r="R22" s="44" t="str">
         <x:v>作为 stretch target。不要第一批消耗冷邮件，优先找 warm intro。</x:v>
       </x:c>
-      <x:c r="O22" s="44" t="str">
+      <x:c r="S22" s="44" t="str">
         <x:v>https://www.scopely.com/</x:v>
       </x:c>
-      <x:c r="P22" s="44" t="str">
+      <x:c r="T22" s="44" t="str">
         <x:v>https://www.scopely.com/en/news/scopely-to-acquire-niantic-games-business-which-includes-pokemon-go-one-of-the-most-successful-mobile-games-of-all-time</x:v>
       </x:c>
-      <x:c r="Q22" s="45" t="str">
+      <x:c r="U22" s="44" t="str">
         <x:v>https://www.pocketgamer.biz/the-top-50-mobile-game-makers-of-2024/</x:v>
       </x:c>
-    </x:row>
-    <x:row r="23" ht="36" hidden="0" customHeight="1">
+      <x:c r="V22" s="45" t="str">
+        <x:v>https://www.scopely.com/en/contact</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="48" hidden="0" customHeight="1">
       <x:c r="A23" s="88" t="str">
         <x:v>22</x:v>
       </x:c>
@@ -1920,37 +2247,52 @@
         <x:v>https://www.zynga.com/</x:v>
       </x:c>
       <x:c r="G23" s="44" t="str">
+        <x:v>Take-Two 2022 以约 $12.7B 收购 Zynga；移动游戏大集团部门。</x:v>
+      </x:c>
+      <x:c r="H23" s="44" t="str">
+        <x:v>FarmVille, Words With Friends, CSR Racing, Empires &amp; Puzzles, Merge Dragons!, Toon Blast, Match Factory!</x:v>
+      </x:c>
+      <x:c r="I23" s="44" t="str">
+        <x:v>Press@zynga.com</x:v>
+      </x:c>
+      <x:c r="J23" s="44" t="str">
+        <x:v>Take-Two/Zynga 合并公告公开 Press@；商务/Corp Dev 建议 Take-Two 路径和 warm intro。</x:v>
+      </x:c>
+      <x:c r="K23" s="44" t="str">
         <x:v>战略上限参照</x:v>
       </x:c>
-      <x:c r="H23" s="44" t="str">
+      <x:c r="L23" s="44" t="str">
         <x:v>北美移动游戏巨头/大集团移动部门，地位高于三七互娱式对标；但有成熟移动发行、并购和 IP 资源。</x:v>
       </x:c>
-      <x:c r="I23" s="44" t="str">
+      <x:c r="M23" s="44" t="str">
         <x:v>对已验证美国市场的休闲/模拟 F2P 项目理论上相关，但外部项目冷启动门槛高。</x:v>
       </x:c>
-      <x:c r="J23" s="44" t="str">
+      <x:c r="N23" s="44" t="str">
         <x:v>收购；战略合作；发行可能性低</x:v>
       </x:c>
-      <x:c r="K23" s="44" t="str">
+      <x:c r="O23" s="44" t="str">
         <x:v>Take-Two corporate development / Zynga leadership</x:v>
       </x:c>
-      <x:c r="L23" s="44" t="str">
+      <x:c r="P23" s="44" t="str">
         <x:v>官网 / LinkedIn / 投资银行或行业转介绍</x:v>
       </x:c>
-      <x:c r="M23" s="89" t="str">
+      <x:c r="Q23" s="89" t="str">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="N23" s="44" t="str">
+      <x:c r="R23" s="44" t="str">
         <x:v>作为 stretch target。除非有强引荐或数据很突出，否则排在 Tilting Point/Jam City 后。</x:v>
       </x:c>
-      <x:c r="O23" s="44" t="str">
+      <x:c r="S23" s="44" t="str">
         <x:v>https://www.zynga.com/</x:v>
       </x:c>
-      <x:c r="P23" s="44" t="str">
+      <x:c r="T23" s="44" t="str">
         <x:v>https://www.take2games.com/ir/news/take-two-interactive-software-inc-completes-combination-with-zynga-inc</x:v>
       </x:c>
-      <x:c r="Q23" s="45" t="str">
+      <x:c r="U23" s="44" t="str">
         <x:v>https://www.take2games.com/</x:v>
+      </x:c>
+      <x:c r="V23" s="45" t="str">
+        <x:v>https://ir.take2games.com/node/28346/pdf</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="36" hidden="0" customHeight="1">
@@ -1973,37 +2315,52 @@
         <x:v>https://www.sciplay.com/</x:v>
       </x:c>
       <x:c r="G24" s="44" t="str">
+        <x:v>Light &amp; Wonder 2023 收购 SciPlay 剩余股权；SciPlay 曾为上市社交 casino 公司。</x:v>
+      </x:c>
+      <x:c r="H24" s="44" t="str">
+        <x:v>Jackpot Party Casino, Quick Hit Slots, Gold Fish Casino, MONOPOLY Slots, Bingo Showdown, 88 Fortunes Slots</x:v>
+      </x:c>
+      <x:c r="I24" s="44" t="str">
+        <x:v>ir@lnw.com</x:v>
+      </x:c>
+      <x:c r="J24" s="44" t="str">
+        <x:v>Light &amp; Wonder/SciPlay 交易资料公开 IR 邮箱；游戏合作更适合 L&amp;W Digital/LinkedIn。</x:v>
+      </x:c>
+      <x:c r="K24" s="44" t="str">
         <x:v>社交娱乐场/移动游戏公司</x:v>
       </x:c>
-      <x:c r="H24" s="44" t="str">
+      <x:c r="L24" s="44" t="str">
         <x:v>美国社交 casino 和 casual mobile 上市/集团型玩家，资金和运营能力强，但品类偏社交娱乐场。</x:v>
       </x:c>
-      <x:c r="I24" s="44" t="str">
+      <x:c r="M24" s="44" t="str">
         <x:v>Family Island 类游戏与其核心品类有距离，但休闲用户、LiveOps 和美国市场验证可作为切入点。</x:v>
       </x:c>
-      <x:c r="J24" s="44" t="str">
+      <x:c r="N24" s="44" t="str">
         <x:v>收购；战略投资；发行合作可能性中低</x:v>
       </x:c>
-      <x:c r="K24" s="44" t="str">
+      <x:c r="O24" s="44" t="str">
         <x:v>Corporate Development / Light &amp; Wonder digital leadership</x:v>
       </x:c>
-      <x:c r="L24" s="44" t="str">
+      <x:c r="P24" s="44" t="str">
         <x:v>官网 contact / investor relations / LinkedIn</x:v>
       </x:c>
-      <x:c r="M24" s="89" t="str">
+      <x:c r="Q24" s="89" t="str">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="N24" s="44" t="str">
+      <x:c r="R24" s="44" t="str">
         <x:v>第三波触达。除非游戏变现偏广告/社交 casino，否则优先级低于休闲模拟发行商。</x:v>
       </x:c>
-      <x:c r="O24" s="44" t="str">
+      <x:c r="S24" s="44" t="str">
         <x:v>https://www.sciplay.com/</x:v>
       </x:c>
-      <x:c r="P24" s="44" t="str">
+      <x:c r="T24" s="44" t="str">
         <x:v>https://www.sciplay.com/games/</x:v>
       </x:c>
-      <x:c r="Q24" s="45" t="str">
+      <x:c r="U24" s="44" t="str">
         <x:v>https://www.lnw.com/company/sciplay/</x:v>
+      </x:c>
+      <x:c r="V24" s="45" t="str">
+        <x:v>https://s202.q4cdn.com/259407146/files/doc_news/2023/05/may-18-23-pr.pdf</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="36" hidden="0" customHeight="1">
@@ -2026,37 +2383,52 @@
         <x:v>https://lsvp.com/sectors/gaming/</x:v>
       </x:c>
       <x:c r="G25" s="44" t="str">
+        <x:v>Lightspeed 为全球多阶段 VC，公开资料显示 backed 500+ companies，资金规模为数百亿美元级。</x:v>
+      </x:c>
+      <x:c r="H25" s="44" t="str">
+        <x:v>投资/组合：Epic Games, Snap, Stability AI, Polygon, Alchemy, Multiverse, gaming/consumer portfolio</x:v>
+      </x:c>
+      <x:c r="I25" s="44" t="str">
+        <x:v>mp-reception@lsvp.com; legal@lsvp.com</x:v>
+      </x:c>
+      <x:c r="J25" s="44" t="str">
+        <x:v>官网 US office 页公开 mp-reception@；legal@ 仅法律事务。</x:v>
+      </x:c>
+      <x:c r="K25" s="44" t="str">
         <x:v>大型 VC 游戏投资线</x:v>
       </x:c>
-      <x:c r="H25" s="44" t="str">
+      <x:c r="L25" s="44" t="str">
         <x:v>Lightspeed 的游戏投资线在北美有影响力；不是游戏发行商，但能做融资和高质量转介。</x:v>
       </x:c>
-      <x:c r="I25" s="44" t="str">
+      <x:c r="M25" s="44" t="str">
         <x:v>适合数据达到融资门槛、需要桥接资金和发行商网络时触达。</x:v>
       </x:c>
-      <x:c r="J25" s="44" t="str">
+      <x:c r="N25" s="44" t="str">
         <x:v>股权投资；战略转介</x:v>
       </x:c>
-      <x:c r="K25" s="44" t="str">
+      <x:c r="O25" s="44" t="str">
         <x:v>Gaming investment partners</x:v>
       </x:c>
-      <x:c r="L25" s="44" t="str">
+      <x:c r="P25" s="44" t="str">
         <x:v>官网 / partner LinkedIn / portfolio warm intro</x:v>
       </x:c>
-      <x:c r="M25" s="89" t="str">
+      <x:c r="Q25" s="89" t="str">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="N25" s="44" t="str">
+      <x:c r="R25" s="44" t="str">
         <x:v>第三波投资线。需要把 KPI 和资金用途压缩成 1-page investor memo。</x:v>
       </x:c>
-      <x:c r="O25" s="44" t="str">
+      <x:c r="S25" s="44" t="str">
         <x:v>https://lsvp.com/sectors/gaming/</x:v>
       </x:c>
-      <x:c r="P25" s="44" t="str">
+      <x:c r="T25" s="44" t="str">
         <x:v>https://lsvp.com/portfolio/</x:v>
       </x:c>
-      <x:c r="Q25" s="45" t="str">
+      <x:c r="U25" s="44" t="str">
         <x:v>https://lsvp.com/team/</x:v>
+      </x:c>
+      <x:c r="V25" s="45" t="str">
+        <x:v>https://lsvp.com/global-presence/lightspeed-united-states/</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="36" hidden="0" customHeight="1">
@@ -2079,37 +2451,52 @@
         <x:v>https://www.sunblink.com/</x:v>
       </x:c>
       <x:c r="G26" s="44" t="str">
+        <x:v>LinkedIn 显示 11-50 人；Boulder 小型 cozy/life-sim 工作室。</x:v>
+      </x:c>
+      <x:c r="H26" s="44" t="str">
+        <x:v>Hello Kitty Island Adventure</x:v>
+      </x:c>
+      <x:c r="I26" s="44" t="str">
+        <x:v>support@sunblink.com; sunblink@fortyseven.com</x:v>
+      </x:c>
+      <x:c r="J26" s="44" t="str">
+        <x:v>Steam 官方支持页列 support@；官网/社区资料可见 sunblink@fortyseven.com。</x:v>
+      </x:c>
+      <x:c r="K26" s="44" t="str">
         <x:v>cozy/life-sim 工作室</x:v>
       </x:c>
-      <x:c r="H26" s="44" t="str">
+      <x:c r="L26" s="44" t="str">
         <x:v>小到中型工作室，因 Hello Kitty Island Adventure 在 cozy/life-sim 方向具备可比经验，但不是典型发行商。</x:v>
       </x:c>
-      <x:c r="I26" s="44" t="str">
+      <x:c r="M26" s="44" t="str">
         <x:v>玩法情绪和人群接近，适合行业交流、联合开发或转介绍，不适合作为主要收购买方。</x:v>
       </x:c>
-      <x:c r="J26" s="44" t="str">
+      <x:c r="N26" s="44" t="str">
         <x:v>联合开发；行业转介绍；小规模合作</x:v>
       </x:c>
-      <x:c r="K26" s="44" t="str">
+      <x:c r="O26" s="44" t="str">
         <x:v>Founder / studio leadership</x:v>
       </x:c>
-      <x:c r="L26" s="44" t="str">
+      <x:c r="P26" s="44" t="str">
         <x:v>官网 / LinkedIn</x:v>
       </x:c>
-      <x:c r="M26" s="89" t="str">
+      <x:c r="Q26" s="89" t="str">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="N26" s="44" t="str">
+      <x:c r="R26" s="44" t="str">
         <x:v>第三波触达。语气偏合作和交流，少谈急迫融资。</x:v>
       </x:c>
-      <x:c r="O26" s="44" t="str">
+      <x:c r="S26" s="44" t="str">
         <x:v>https://www.sunblink.com/</x:v>
       </x:c>
-      <x:c r="P26" s="44" t="str">
+      <x:c r="T26" s="44" t="str">
         <x:v>https://www.sunblink.com/games</x:v>
       </x:c>
-      <x:c r="Q26" s="45" t="str">
+      <x:c r="U26" s="44" t="str">
         <x:v>https://www.apple.com/newsroom/2023/07/hello-kitty-island-adventure-launches-on-apple-arcade/</x:v>
+      </x:c>
+      <x:c r="V26" s="45" t="str">
+        <x:v>https://help.steampowered.com/en/wizard/HelpWithGameTechnicalIssue?appid=2495100</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="36" hidden="0" customHeight="1">
@@ -2132,40 +2519,55 @@
         <x:v>https://www.rogueco.com/</x:v>
       </x:c>
       <x:c r="G27" s="44" t="str">
+        <x:v>美国独立发行商；Steam/官网 portfolio 覆盖数十款 premium/indie titles。</x:v>
+      </x:c>
+      <x:c r="H27" s="44" t="str">
+        <x:v>Dust &amp; Neon, The Last Case of Benedict Fox, Wipeout Rush, Sprawl, Arcanium, Wonderputt Forever</x:v>
+      </x:c>
+      <x:c r="I27" s="44" t="str">
+        <x:v>未找到公开邮箱；使用官网 Developer / BD / Media contact forms</x:v>
+      </x:c>
+      <x:c r="J27" s="44" t="str">
+        <x:v>官网 Contact 页按 Player/Developer/Media/BD 分流，但不直接列邮箱。</x:v>
+      </x:c>
+      <x:c r="K27" s="44" t="str">
         <x:v>独立游戏发行商</x:v>
       </x:c>
-      <x:c r="H27" s="44" t="str">
+      <x:c r="L27" s="44" t="str">
         <x:v>美国独立发行商，覆盖 PC/console/mobile，但不是移动休闲头部。</x:v>
       </x:c>
-      <x:c r="I27" s="44" t="str">
+      <x:c r="M27" s="44" t="str">
         <x:v>如果项目可以包装为跨平台 cozy/adventure，可能有讨论空间；纯移动 F2P 买量能力需验证。</x:v>
       </x:c>
-      <x:c r="J27" s="44" t="str">
+      <x:c r="N27" s="44" t="str">
         <x:v>发行；联合开发；平台发行</x:v>
       </x:c>
-      <x:c r="K27" s="44" t="str">
+      <x:c r="O27" s="44" t="str">
         <x:v>Publishing / Business Development</x:v>
       </x:c>
-      <x:c r="L27" s="44" t="str">
+      <x:c r="P27" s="44" t="str">
         <x:v>官网 contact / LinkedIn</x:v>
       </x:c>
-      <x:c r="M27" s="89" t="str">
+      <x:c r="Q27" s="89" t="str">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="N27" s="44" t="str">
+      <x:c r="R27" s="44" t="str">
         <x:v>第三波触达。若游戏仍是纯移动 F2P，优先级低于 Tilting Point 和 Jam City。</x:v>
       </x:c>
-      <x:c r="O27" s="44" t="str">
+      <x:c r="S27" s="44" t="str">
         <x:v>https://www.rogueco.com/</x:v>
       </x:c>
-      <x:c r="P27" s="44" t="str">
+      <x:c r="T27" s="44" t="str">
         <x:v>https://www.rogueco.com/games</x:v>
       </x:c>
-      <x:c r="Q27" s="45" t="str">
+      <x:c r="U27" s="44" t="str">
         <x:v>https://www.rogueco.com/contact</x:v>
       </x:c>
-    </x:row>
-    <x:row r="28" ht="24" hidden="0" customHeight="1">
+      <x:c r="V27" s="45" t="str">
+        <x:v>https://rogueco.com/contact/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="36" hidden="0" customHeight="1">
       <x:c r="A28" s="88" t="str">
         <x:v>27</x:v>
       </x:c>
@@ -2185,40 +2587,55 @@
         <x:v>https://www.galaxy.com/interactive/</x:v>
       </x:c>
       <x:c r="G28" s="44" t="str">
+        <x:v>Galaxy Interactive 公开披露 $650M AUM across two funds、75+ portfolio companies。</x:v>
+      </x:c>
+      <x:c r="H28" s="44" t="str">
+        <x:v>投资/组合：Mythical Games, Genvid, Immutable, GreenPark, StockX, Bad Robot Games, 1047 Games</x:v>
+      </x:c>
+      <x:c r="I28" s="44" t="str">
+        <x:v>abuse@galaxy.com; media contact form</x:v>
+      </x:c>
+      <x:c r="J28" s="44" t="str">
+        <x:v>官网只公开 abuse@ 用于可疑邮件上报；投资/媒体建议用官网 Contact/LinkedIn。</x:v>
+      </x:c>
+      <x:c r="K28" s="44" t="str">
         <x:v>游戏/互动娱乐投资机构</x:v>
       </x:c>
-      <x:c r="H28" s="44" t="str">
+      <x:c r="L28" s="44" t="str">
         <x:v>互动娱乐、游戏和数字资产相关投资平台，适合融资线补充。</x:v>
       </x:c>
-      <x:c r="I28" s="44" t="str">
+      <x:c r="M28" s="44" t="str">
         <x:v>不适合只谈发行；适合把项目作为互动娱乐/游戏团队融资机会递交。</x:v>
       </x:c>
-      <x:c r="J28" s="44" t="str">
+      <x:c r="N28" s="44" t="str">
         <x:v>股权投资；战略转介</x:v>
       </x:c>
-      <x:c r="K28" s="44" t="str">
+      <x:c r="O28" s="44" t="str">
         <x:v>Investment team</x:v>
       </x:c>
-      <x:c r="L28" s="44" t="str">
+      <x:c r="P28" s="44" t="str">
         <x:v>官网 / LinkedIn / portfolio warm intro</x:v>
       </x:c>
-      <x:c r="M28" s="89" t="str">
+      <x:c r="Q28" s="89" t="str">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="N28" s="44" t="str">
+      <x:c r="R28" s="44" t="str">
         <x:v>第三波投资线。若产品指标不错但缺少发行方，作为备选融资入口。</x:v>
       </x:c>
-      <x:c r="O28" s="44" t="str">
+      <x:c r="S28" s="44" t="str">
         <x:v>https://www.galaxy.com/interactive/</x:v>
       </x:c>
-      <x:c r="P28" s="44" t="str">
+      <x:c r="T28" s="44" t="str">
         <x:v>https://www.galaxy.com/businesses/galaxy-ventures/</x:v>
       </x:c>
-      <x:c r="Q28" s="45" t="str">
+      <x:c r="U28" s="44" t="str">
         <x:v>https://www.galaxy.com/</x:v>
       </x:c>
-    </x:row>
-    <x:row r="29" ht="24" hidden="0" customHeight="1">
+      <x:c r="V28" s="45" t="str">
+        <x:v>https://interactive.galaxy.com/contact/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="36" hidden="0" customHeight="1">
       <x:c r="A29" s="88" t="str">
         <x:v>28</x:v>
       </x:c>
@@ -2238,37 +2655,52 @@
         <x:v>https://www.productmadness.com/</x:v>
       </x:c>
       <x:c r="G29" s="44" t="str">
+        <x:v>Aristocrat 旗下全球 social casino mobile studio；公开招聘资料显示 550+ employees/501-1000 人级。</x:v>
+      </x:c>
+      <x:c r="H29" s="44" t="str">
+        <x:v>Heart of Vegas, Cashman Casino, Lightning Link Casino, FaFaFa Gold, Big Fish Casino</x:v>
+      </x:c>
+      <x:c r="I29" s="44" t="str">
+        <x:v>support@productmadness.com; mobile@productmadness.com</x:v>
+      </x:c>
+      <x:c r="J29" s="44" t="str">
+        <x:v>官网 TOS 公开 support@；第三方资料列 mobile@，商务需核验。</x:v>
+      </x:c>
+      <x:c r="K29" s="44" t="str">
         <x:v>社交 casino 移动公司</x:v>
       </x:c>
-      <x:c r="H29" s="44" t="str">
+      <x:c r="L29" s="44" t="str">
         <x:v>Aristocrat 旗下社交 casino 移动游戏公司，资金和运营强，但品类偏差较大。</x:v>
       </x:c>
-      <x:c r="I29" s="44" t="str">
+      <x:c r="M29" s="44" t="str">
         <x:v>除非项目变现更偏广告/社交娱乐场用户，否则仅作为拓展名单。</x:v>
       </x:c>
-      <x:c r="J29" s="44" t="str">
+      <x:c r="N29" s="44" t="str">
         <x:v>收购；战略合作；发行可能性低</x:v>
       </x:c>
-      <x:c r="K29" s="44" t="str">
+      <x:c r="O29" s="44" t="str">
         <x:v>Aristocrat digital / Product Madness leadership</x:v>
       </x:c>
-      <x:c r="L29" s="44" t="str">
+      <x:c r="P29" s="44" t="str">
         <x:v>官网 contact / LinkedIn</x:v>
       </x:c>
-      <x:c r="M29" s="89" t="str">
+      <x:c r="Q29" s="89" t="str">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="N29" s="44" t="str">
+      <x:c r="R29" s="44" t="str">
         <x:v>第三波后段触达。话术重点放在美国用户验证和休闲运营，不要强调 farming sim。</x:v>
       </x:c>
-      <x:c r="O29" s="44" t="str">
+      <x:c r="S29" s="44" t="str">
         <x:v>https://www.productmadness.com/</x:v>
       </x:c>
-      <x:c r="P29" s="44" t="str">
+      <x:c r="T29" s="44" t="str">
         <x:v>https://www.productmadness.com/games/</x:v>
       </x:c>
-      <x:c r="Q29" s="45" t="str">
+      <x:c r="U29" s="44" t="str">
         <x:v>https://www.aristocrat.com/businesses/product-madness/</x:v>
+      </x:c>
+      <x:c r="V29" s="45" t="str">
+        <x:v>https://www.productmadness.com/terms-of-service/</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="36" hidden="0" customHeight="1">
@@ -2291,40 +2723,55 @@
         <x:v>https://armorgamesstudios.com/</x:v>
       </x:c>
       <x:c r="G30" s="44" t="str">
+        <x:v>老牌 web/indie 发行品牌；ArmorGames.com 长期运营，2024 年后 publishing team 状态需核验。</x:v>
+      </x:c>
+      <x:c r="H30" s="44" t="str">
+        <x:v>Bear and Breakfast, The Last Stand: Aftermath, Soda Dungeon, GemCraft, Sonny, Infernax</x:v>
+      </x:c>
+      <x:c r="I30" s="44" t="str">
+        <x:v>未找到公开商务邮箱；使用官网 Contact/Publisher inquiry form</x:v>
+      </x:c>
+      <x:c r="J30" s="44" t="str">
+        <x:v>官网 Contact 页面向 developers，但不直接列邮箱。</x:v>
+      </x:c>
+      <x:c r="K30" s="44" t="str">
         <x:v>独立发行商</x:v>
       </x:c>
-      <x:c r="H30" s="44" t="str">
+      <x:c r="L30" s="44" t="str">
         <x:v>美国独立游戏发行商，有 web/PC/console/mobile 历史，但不是移动买量发行商。</x:v>
       </x:c>
-      <x:c r="I30" s="44" t="str">
+      <x:c r="M30" s="44" t="str">
         <x:v>若游戏可转为 premium/cozy 或多平台体验，可能有发行讨论；纯 F2P 移动项目适配一般。</x:v>
       </x:c>
-      <x:c r="J30" s="44" t="str">
+      <x:c r="N30" s="44" t="str">
         <x:v>发行；平台合作；联合开发</x:v>
       </x:c>
-      <x:c r="K30" s="44" t="str">
+      <x:c r="O30" s="44" t="str">
         <x:v>Publishing / submissions</x:v>
       </x:c>
-      <x:c r="L30" s="44" t="str">
+      <x:c r="P30" s="44" t="str">
         <x:v>官网 submission / contact</x:v>
       </x:c>
-      <x:c r="M30" s="89" t="str">
+      <x:c r="Q30" s="89" t="str">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="N30" s="44" t="str">
+      <x:c r="R30" s="44" t="str">
         <x:v>第三波触达。适合拿来拓展，但不是解决现金流的首要对象。</x:v>
       </x:c>
-      <x:c r="O30" s="44" t="str">
+      <x:c r="S30" s="44" t="str">
         <x:v>https://armorgamesstudios.com/</x:v>
       </x:c>
-      <x:c r="P30" s="44" t="str">
+      <x:c r="T30" s="44" t="str">
         <x:v>https://armorgamesstudios.com/games/</x:v>
       </x:c>
-      <x:c r="Q30" s="45" t="str">
+      <x:c r="U30" s="44" t="str">
         <x:v>https://armorgamesstudios.com/contact/</x:v>
       </x:c>
-    </x:row>
-    <x:row r="31" ht="24" hidden="0" customHeight="1">
+      <x:c r="V30" s="45" t="str">
+        <x:v>https://armorgamesstudios.com/contact</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="48" hidden="0" customHeight="1">
       <x:c r="A31" s="88" t="str">
         <x:v>30</x:v>
       </x:c>
@@ -2344,40 +2791,53 @@
         <x:v>https://gamemill.com/</x:v>
       </x:c>
       <x:c r="G31" s="44" t="str">
+        <x:v>官网披露 50+ years combined experience、millions of units sold、global publishing partner。</x:v>
+      </x:c>
+      <x:c r="H31" s="44" t="str">
+        <x:v>Nickelodeon All-Star Brawl 2, Nickelodeon Kart Racers, Hot Wheels Monster Trucks, The Walking Dead Destinies, Avatar: The Last Airbender: Quest for Balance</x:v>
+      </x:c>
+      <x:c r="I31" s="44" t="str">
+        <x:v>未找到公开邮箱；使用官网 Developer Contact / Licensor Contact forms</x:v>
+      </x:c>
+      <x:c r="J31" s="44" t="str">
+        <x:v>官网 Contact 页分 Developer/Licensor opportunities，但不直接列邮箱。</x:v>
+      </x:c>
+      <x:c r="K31" s="44" t="str">
         <x:v>授权/IP 游戏发行商</x:v>
       </x:c>
-      <x:c r="H31" s="44" t="str">
+      <x:c r="L31" s="44" t="str">
         <x:v>美国授权/IP 游戏发行商，更多偏 console/PC/licensed games，不是典型移动休闲发行商。</x:v>
       </x:c>
-      <x:c r="I31" s="44" t="str">
+      <x:c r="M31" s="44" t="str">
         <x:v>除非项目可以绑定 IP 或多平台化，否则适配度一般。</x:v>
       </x:c>
-      <x:c r="J31" s="44" t="str">
+      <x:c r="N31" s="44" t="str">
         <x:v>发行；IP合作；项目合作</x:v>
       </x:c>
-      <x:c r="K31" s="44" t="str">
+      <x:c r="O31" s="44" t="str">
         <x:v>Publishing / licensing</x:v>
       </x:c>
-      <x:c r="L31" s="44" t="str">
+      <x:c r="P31" s="44" t="str">
         <x:v>官网 contact / LinkedIn</x:v>
       </x:c>
-      <x:c r="M31" s="89" t="str">
+      <x:c r="Q31" s="89" t="str">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="N31" s="44" t="str">
+      <x:c r="R31" s="44" t="str">
         <x:v>第三波后段触达。可以作为 IP/发行资源补充。</x:v>
       </x:c>
-      <x:c r="O31" s="44" t="str">
+      <x:c r="S31" s="44" t="str">
         <x:v>https://gamemill.com/</x:v>
       </x:c>
-      <x:c r="P31" s="44" t="str">
+      <x:c r="T31" s="44" t="str">
         <x:v>https://gamemill.com/games/</x:v>
       </x:c>
-      <x:c r="Q31" s="45" t="str">
+      <x:c r="U31" s="44" t="str">
         <x:v>https://gamemill.com/contact/</x:v>
       </x:c>
-    </x:row>
-    <x:row r="32" ht="24" hidden="0" customHeight="1">
+      <x:c r="V31" s="45" t="str"/>
+    </x:row>
+    <x:row r="32" ht="36" hidden="0" customHeight="1">
       <x:c r="A32" s="88" t="str">
         <x:v>31</x:v>
       </x:c>
@@ -2397,40 +2857,55 @@
         <x:v>https://www.skybound.com/games</x:v>
       </x:c>
       <x:c r="G32" s="44" t="str">
+        <x:v>Skybound Entertainment 游戏发行部门；IP/creator-led publisher，母公司覆盖 comics/TV/games。</x:v>
+      </x:c>
+      <x:c r="H32" s="44" t="str">
+        <x:v>The Walking Dead: The Telltale Definitive Series, WrestleQuest, Before Your Eyes, Invincible Presents: Atom Eve, Glitch Busters</x:v>
+      </x:c>
+      <x:c r="I32" s="44" t="str">
+        <x:v>swynne@skybound.com; webstore@skybound.com</x:v>
+      </x:c>
+      <x:c r="J32" s="44" t="str">
+        <x:v>公开新闻稿列 PR 联系 swynne@；webstore@ 为商店支持，不适合 BD。</x:v>
+      </x:c>
+      <x:c r="K32" s="44" t="str">
         <x:v>IP/独立游戏发行商</x:v>
       </x:c>
-      <x:c r="H32" s="44" t="str">
+      <x:c r="L32" s="44" t="str">
         <x:v>Skybound 具备 IP 和游戏发行能力，但重心不在移动 F2P 发行。</x:v>
       </x:c>
-      <x:c r="I32" s="44" t="str">
+      <x:c r="M32" s="44" t="str">
         <x:v>若项目能往 IP/cozy adventure 方向包装，可试探；否则不是优先买方。</x:v>
       </x:c>
-      <x:c r="J32" s="44" t="str">
+      <x:c r="N32" s="44" t="str">
         <x:v>发行；IP合作；联合开发</x:v>
       </x:c>
-      <x:c r="K32" s="44" t="str">
+      <x:c r="O32" s="44" t="str">
         <x:v>Games publishing / business development</x:v>
       </x:c>
-      <x:c r="L32" s="44" t="str">
+      <x:c r="P32" s="44" t="str">
         <x:v>官网 / LinkedIn</x:v>
       </x:c>
-      <x:c r="M32" s="89" t="str">
+      <x:c r="Q32" s="89" t="str">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="N32" s="44" t="str">
+      <x:c r="R32" s="44" t="str">
         <x:v>第三波后段。更适合平台发行或 IP 合作口径。</x:v>
       </x:c>
-      <x:c r="O32" s="44" t="str">
+      <x:c r="S32" s="44" t="str">
         <x:v>https://www.skybound.com/games</x:v>
       </x:c>
-      <x:c r="P32" s="44" t="str">
+      <x:c r="T32" s="44" t="str">
         <x:v>https://www.skybound.com/about</x:v>
       </x:c>
-      <x:c r="Q32" s="45" t="str">
+      <x:c r="U32" s="44" t="str">
         <x:v>https://www.skybound.com/contact</x:v>
       </x:c>
-    </x:row>
-    <x:row r="33" ht="24" hidden="0" customHeight="1">
+      <x:c r="V32" s="45" t="str">
+        <x:v>https://mb.cision.com/Main/14632/2410871/764821.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="36" hidden="0" customHeight="1">
       <x:c r="A33" s="88" t="str">
         <x:v>32</x:v>
       </x:c>
@@ -2450,40 +2925,55 @@
         <x:v>https://www.doubledowninteractive.com/</x:v>
       </x:c>
       <x:c r="G33" s="44" t="str">
+        <x:v>纳斯达克上市/韩国控股 social casino 公司；公开 IR 资料为上市公司级别。</x:v>
+      </x:c>
+      <x:c r="H33" s="44" t="str">
+        <x:v>DoubleDown Casino, DoubleDown Fort Knox, DoubleDown Classic Slots, Ellen's Road to Riches</x:v>
+      </x:c>
+      <x:c r="I33" s="44" t="str">
+        <x:v>IR@doubledown.com; DDI@jcir.com; support@doubledowncasino.com</x:v>
+      </x:c>
+      <x:c r="J33" s="44" t="str">
+        <x:v>IR 页面公开公司 IR 与 JCIR 邮箱；玩家支持用 support@。</x:v>
+      </x:c>
+      <x:c r="K33" s="44" t="str">
         <x:v>社交 casino 移动公司</x:v>
       </x:c>
-      <x:c r="H33" s="44" t="str">
+      <x:c r="L33" s="44" t="str">
         <x:v>社交 casino 发行/运营公司，公开上市，资金能力有但品类偏差较大。</x:v>
       </x:c>
-      <x:c r="I33" s="44" t="str">
+      <x:c r="M33" s="44" t="str">
         <x:v>只适合作为低优先级拓展；项目需强调休闲用户和美国指标，而不是玩法相似。</x:v>
       </x:c>
-      <x:c r="J33" s="44" t="str">
+      <x:c r="N33" s="44" t="str">
         <x:v>收购；战略合作；投资可能性低</x:v>
       </x:c>
-      <x:c r="K33" s="44" t="str">
+      <x:c r="O33" s="44" t="str">
         <x:v>Corporate Development / IR / leadership</x:v>
       </x:c>
-      <x:c r="L33" s="44" t="str">
+      <x:c r="P33" s="44" t="str">
         <x:v>官网 contact / IR</x:v>
       </x:c>
-      <x:c r="M33" s="89" t="str">
+      <x:c r="Q33" s="89" t="str">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="N33" s="44" t="str">
+      <x:c r="R33" s="44" t="str">
         <x:v>第三波后段。若没有社交 casino 关系，暂缓。</x:v>
       </x:c>
-      <x:c r="O33" s="44" t="str">
+      <x:c r="S33" s="44" t="str">
         <x:v>https://www.doubledowninteractive.com/</x:v>
       </x:c>
-      <x:c r="P33" s="44" t="str">
+      <x:c r="T33" s="44" t="str">
         <x:v>https://ir.doubledowninteractive.com/</x:v>
       </x:c>
-      <x:c r="Q33" s="45" t="str">
+      <x:c r="U33" s="44" t="str">
         <x:v>https://www.doubledowninteractive.com/games/</x:v>
       </x:c>
-    </x:row>
-    <x:row r="34" ht="24" hidden="0" customHeight="1">
+      <x:c r="V33" s="45" t="str">
+        <x:v>https://ir.doubledowninteractive.com/ir-services/contact-ir?mobile=1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="36" hidden="0" customHeight="1">
       <x:c r="A34" s="88" t="str">
         <x:v>33</x:v>
       </x:c>
@@ -2503,40 +2993,55 @@
         <x:v>https://maximument.com/</x:v>
       </x:c>
       <x:c r="G34" s="44" t="str">
+        <x:v>上市多平台发行/开发集团；Maximum/Modus/Merge/Just For Games 整合后运营。</x:v>
+      </x:c>
+      <x:c r="H34" s="44" t="str">
+        <x:v>Squirrel with a Gun, Diesel Legacy, Trine 5, Afterimage, Smalland, Them's Fightin' Herds, Double Dragon Gaiden</x:v>
+      </x:c>
+      <x:c r="I34" s="44" t="str">
+        <x:v>ir@maximument.com</x:v>
+      </x:c>
+      <x:c r="J34" s="44" t="str">
+        <x:v>官网 Contact 页公开 IR 邮箱；一般/发行合作主要走表单。</x:v>
+      </x:c>
+      <x:c r="K34" s="44" t="str">
         <x:v>中型多平台发行商</x:v>
       </x:c>
-      <x:c r="H34" s="44" t="str">
+      <x:c r="L34" s="44" t="str">
         <x:v>多平台发行商，偏 PC/console 和 indie/AA，不是移动 F2P 发行核心。</x:v>
       </x:c>
-      <x:c r="I34" s="44" t="str">
+      <x:c r="M34" s="44" t="str">
         <x:v>若项目有多平台化或 premium 版本路径，可进入讨论；纯移动买量合作适配一般。</x:v>
       </x:c>
-      <x:c r="J34" s="44" t="str">
+      <x:c r="N34" s="44" t="str">
         <x:v>发行；联合开发；平台发行</x:v>
       </x:c>
-      <x:c r="K34" s="44" t="str">
+      <x:c r="O34" s="44" t="str">
         <x:v>Publishing / submissions</x:v>
       </x:c>
-      <x:c r="L34" s="44" t="str">
+      <x:c r="P34" s="44" t="str">
         <x:v>官网 contact / LinkedIn</x:v>
       </x:c>
-      <x:c r="M34" s="89" t="str">
+      <x:c r="Q34" s="89" t="str">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="N34" s="44" t="str">
+      <x:c r="R34" s="44" t="str">
         <x:v>低优先级。除非产品策略准备做多平台。</x:v>
       </x:c>
-      <x:c r="O34" s="44" t="str">
+      <x:c r="S34" s="44" t="str">
         <x:v>https://maximument.com/</x:v>
       </x:c>
-      <x:c r="P34" s="44" t="str">
+      <x:c r="T34" s="44" t="str">
         <x:v>https://modusgames.com/</x:v>
       </x:c>
-      <x:c r="Q34" s="45" t="str">
+      <x:c r="U34" s="44" t="str">
         <x:v>https://maximument.com/games/</x:v>
       </x:c>
-    </x:row>
-    <x:row r="35" ht="24" hidden="0" customHeight="1">
+      <x:c r="V34" s="45" t="str">
+        <x:v>https://maximument.com/contact/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="48" hidden="0" customHeight="1">
       <x:c r="A35" s="88" t="str">
         <x:v>34</x:v>
       </x:c>
@@ -2556,37 +3061,52 @@
         <x:v>https://www.hirezstudios.com/</x:v>
       </x:c>
       <x:c r="G35" s="44" t="str">
+        <x:v>公开资料显示 450+ employees；F2P games-as-a-service 工作室。</x:v>
+      </x:c>
+      <x:c r="H35" s="44" t="str">
+        <x:v>SMITE, Paladins, Rogue Company, Realm Royale, Tribes: Ascend, Divine Knockout</x:v>
+      </x:c>
+      <x:c r="I35" s="44" t="str">
+        <x:v>info@hirezstudios.com; bizdev@hirezstudios.com; pr@hirezstudios.com; legal@hirezstudios.com</x:v>
+      </x:c>
+      <x:c r="J35" s="44" t="str">
+        <x:v>公开资料列 info/bizdev；官网隐私文件列 legal@；需先验证当前响应性。</x:v>
+      </x:c>
+      <x:c r="K35" s="44" t="str">
         <x:v>F2P 在线游戏开发发行商</x:v>
       </x:c>
-      <x:c r="H35" s="44" t="str">
+      <x:c r="L35" s="44" t="str">
         <x:v>美国 F2P 在线游戏公司，强项在多人竞技和 live service，不是休闲模拟。</x:v>
       </x:c>
-      <x:c r="I35" s="44" t="str">
+      <x:c r="M35" s="44" t="str">
         <x:v>数据优秀也可试探，但品类差异明显。</x:v>
       </x:c>
-      <x:c r="J35" s="44" t="str">
+      <x:c r="N35" s="44" t="str">
         <x:v>联合开发；发行可能性低；团队合作</x:v>
       </x:c>
-      <x:c r="K35" s="44" t="str">
+      <x:c r="O35" s="44" t="str">
         <x:v>Business Development / leadership</x:v>
       </x:c>
-      <x:c r="L35" s="44" t="str">
+      <x:c r="P35" s="44" t="str">
         <x:v>官网 / LinkedIn</x:v>
       </x:c>
-      <x:c r="M35" s="89" t="str">
+      <x:c r="Q35" s="89" t="str">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="N35" s="44" t="str">
+      <x:c r="R35" s="44" t="str">
         <x:v>仅作备选名单，不进入第一轮。</x:v>
       </x:c>
-      <x:c r="O35" s="44" t="str">
+      <x:c r="S35" s="44" t="str">
         <x:v>https://www.hirezstudios.com/</x:v>
       </x:c>
-      <x:c r="P35" s="44" t="str">
+      <x:c r="T35" s="44" t="str">
         <x:v>https://www.hirezstudios.com/games/</x:v>
       </x:c>
-      <x:c r="Q35" s="45" t="str">
+      <x:c r="U35" s="44" t="str">
         <x:v>https://www.hirezstudios.com/contact/</x:v>
+      </x:c>
+      <x:c r="V35" s="45" t="str">
+        <x:v>https://www.hirezstudios.com/about</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="24" hidden="0" customHeight="1">
@@ -2609,37 +3129,52 @@
         <x:v>https://www.1up.vc/</x:v>
       </x:c>
       <x:c r="G36" s="44" t="str">
+        <x:v>游戏专项早期基金；官网说明标准化投资额/比例，不做 lead investor。</x:v>
+      </x:c>
+      <x:c r="H36" s="44" t="str">
+        <x:v>投资/组合：独立游戏与内容型 studio；具体 portfolio 需在官网逐项核验。</x:v>
+      </x:c>
+      <x:c r="I36" s="44" t="str">
+        <x:v>未找到公开邮箱；使用 1Up Fund 官网 Contact Us / studio submission form</x:v>
+      </x:c>
+      <x:c r="J36" s="44" t="str">
+        <x:v>官网明确让融资团队填表提交，不列通用邮箱。</x:v>
+      </x:c>
+      <x:c r="K36" s="44" t="str">
         <x:v>游戏投资机构</x:v>
       </x:c>
-      <x:c r="H36" s="44" t="str">
+      <x:c r="L36" s="44" t="str">
         <x:v>专注游戏的早期投资基金，规模小于 Griffin/BITKRAFT，但对游戏团队更垂直。</x:v>
       </x:c>
-      <x:c r="I36" s="44" t="str">
+      <x:c r="M36" s="44" t="str">
         <x:v>适合早期融资或买方转介，尤其在资金缺口较小且数据可验证时。</x:v>
       </x:c>
-      <x:c r="J36" s="44" t="str">
+      <x:c r="N36" s="44" t="str">
         <x:v>早期投资；桥接融资；战略转介</x:v>
       </x:c>
-      <x:c r="K36" s="44" t="str">
+      <x:c r="O36" s="44" t="str">
         <x:v>Investment team</x:v>
       </x:c>
-      <x:c r="L36" s="44" t="str">
+      <x:c r="P36" s="44" t="str">
         <x:v>官网 / partner LinkedIn</x:v>
       </x:c>
-      <x:c r="M36" s="89" t="str">
+      <x:c r="Q36" s="89" t="str">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="N36" s="44" t="str">
+      <x:c r="R36" s="44" t="str">
         <x:v>投资线补充对象。适合短邮件和 1-page teaser。</x:v>
       </x:c>
-      <x:c r="O36" s="44" t="str">
+      <x:c r="S36" s="44" t="str">
         <x:v>https://www.1up.vc/</x:v>
       </x:c>
-      <x:c r="P36" s="44" t="str">
+      <x:c r="T36" s="44" t="str">
         <x:v>https://www.1up.vc/portfolio</x:v>
       </x:c>
-      <x:c r="Q36" s="45" t="str">
+      <x:c r="U36" s="44" t="str">
         <x:v>https://www.1up.vc/team</x:v>
+      </x:c>
+      <x:c r="V36" s="45" t="str">
+        <x:v>https://1upfund.com/contact-us/</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="36" hidden="0" customHeight="1">
@@ -2662,40 +3197,55 @@
         <x:v>https://www.ea.com/games/library/mobile</x:v>
       </x:c>
       <x:c r="G37" s="44" t="str">
+        <x:v>EA 为全球大型上市游戏公司；Q2 FY26 公告提及 $55B 私有化交易企业价值；移动部门是集团业务线之一。</x:v>
+      </x:c>
+      <x:c r="H37" s="44" t="str">
+        <x:v>EA SPORTS FC Mobile, Madden NFL Mobile, The Sims Mobile, Plants vs. Zombies, Star Wars: Galaxy of Heroes, Golf Clash</x:v>
+      </x:c>
+      <x:c r="I37" s="44" t="str">
+        <x:v>ir@ea.com; auerkwitz@ea.com; jhiggs@ea.com</x:v>
+      </x:c>
+      <x:c r="J37" s="44" t="str">
+        <x:v>EA IR 页面公开 ir@；财报新闻稿列 IR/Comms 联系人邮箱。</x:v>
+      </x:c>
+      <x:c r="K37" s="44" t="str">
         <x:v>战略上限参照</x:v>
       </x:c>
-      <x:c r="H37" s="44" t="str">
+      <x:c r="L37" s="44" t="str">
         <x:v>北美游戏巨头的移动业务，地位远高于本次对标层级；可作为 stretch target，而不是核心对标。</x:v>
       </x:c>
-      <x:c r="I37" s="44" t="str">
+      <x:c r="M37" s="44" t="str">
         <x:v>除非数据非常好或团队有强引荐，否则冷启动机会低。</x:v>
       </x:c>
-      <x:c r="J37" s="44" t="str">
+      <x:c r="N37" s="44" t="str">
         <x:v>收购；战略合作；发行可能性低</x:v>
       </x:c>
-      <x:c r="K37" s="44" t="str">
+      <x:c r="O37" s="44" t="str">
         <x:v>Corporate Development / EA Mobile leadership</x:v>
       </x:c>
-      <x:c r="L37" s="44" t="str">
+      <x:c r="P37" s="44" t="str">
         <x:v>官网 / LinkedIn / 投行或行业转介绍</x:v>
       </x:c>
-      <x:c r="M37" s="89" t="str">
+      <x:c r="Q37" s="89" t="str">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="N37" s="44" t="str">
+      <x:c r="R37" s="44" t="str">
         <x:v>低优先级 stretch。先做 warm intro，不建议冷邮件首批发送。</x:v>
       </x:c>
-      <x:c r="O37" s="44" t="str">
+      <x:c r="S37" s="44" t="str">
         <x:v>https://www.ea.com/games/library/mobile</x:v>
       </x:c>
-      <x:c r="P37" s="44" t="str">
+      <x:c r="T37" s="44" t="str">
         <x:v>https://www.ea.com/news/electronic-arts-completes-acquisition-of-glu-mobile</x:v>
       </x:c>
-      <x:c r="Q37" s="45" t="str">
+      <x:c r="U37" s="44" t="str">
         <x:v>https://ir.ea.com/</x:v>
       </x:c>
-    </x:row>
-    <x:row r="38" ht="24" hidden="0" customHeight="1">
+      <x:c r="V37" s="45" t="str">
+        <x:v>https://ir.ea.com/resources/connect-with-us/default.aspx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="36" hidden="0" customHeight="1">
       <x:c r="A38" s="88" t="str">
         <x:v>37</x:v>
       </x:c>
@@ -2715,40 +3265,55 @@
         <x:v>https://annapurnainteractive.com/</x:v>
       </x:c>
       <x:c r="G38" s="44" t="str">
+        <x:v>Annapurna Pictures 旗下精品发行 label，2016 年成立；发行 portfolio 覆盖多平台 premium hits。</x:v>
+      </x:c>
+      <x:c r="H38" s="44" t="str">
+        <x:v>Stray, Outer Wilds, Neon White, What Remains of Edith Finch, Journey, Cocoon, Donut County, Kentucky Route Zero</x:v>
+      </x:c>
+      <x:c r="I38" s="44" t="str">
+        <x:v>contact@annapurnainteractive.com; help@annapurnainteractive.com; annapurna@tarabrunopr.com</x:v>
+      </x:c>
+      <x:c r="J38" s="44" t="str">
+        <x:v>官网 About 页公开 general/support/press 邮箱。</x:v>
+      </x:c>
+      <x:c r="K38" s="44" t="str">
         <x:v>精品独立游戏发行商</x:v>
       </x:c>
-      <x:c r="H38" s="44" t="str">
+      <x:c r="L38" s="44" t="str">
         <x:v>美国精品独立发行商，品牌强但不做典型移动 F2P 买量发行。</x:v>
       </x:c>
-      <x:c r="I38" s="44" t="str">
+      <x:c r="M38" s="44" t="str">
         <x:v>如果项目能改造成 premium/cozy narrative 体验才有一定适配；当前 Family Island 类 F2P 适配低。</x:v>
       </x:c>
-      <x:c r="J38" s="44" t="str">
+      <x:c r="N38" s="44" t="str">
         <x:v>平台发行；精品发行；IP/内容合作</x:v>
       </x:c>
-      <x:c r="K38" s="44" t="str">
+      <x:c r="O38" s="44" t="str">
         <x:v>Publishing submissions</x:v>
       </x:c>
-      <x:c r="L38" s="44" t="str">
+      <x:c r="P38" s="44" t="str">
         <x:v>官网 contact / submissions</x:v>
       </x:c>
-      <x:c r="M38" s="89" t="str">
+      <x:c r="Q38" s="89" t="str">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="N38" s="44" t="str">
+      <x:c r="R38" s="44" t="str">
         <x:v>仅作低优先级拓展。除非产品策略变化，不建议进入第一二波。</x:v>
       </x:c>
-      <x:c r="O38" s="44" t="str">
+      <x:c r="S38" s="44" t="str">
         <x:v>https://annapurnainteractive.com/en</x:v>
       </x:c>
-      <x:c r="P38" s="44" t="str">
+      <x:c r="T38" s="44" t="str">
         <x:v>https://annapurnainteractive.com/en/games</x:v>
       </x:c>
-      <x:c r="Q38" s="45" t="str">
+      <x:c r="U38" s="44" t="str">
         <x:v>https://annapurnainteractive.com/en/contact</x:v>
       </x:c>
-    </x:row>
-    <x:row r="39" ht="24" hidden="0" customHeight="1">
+      <x:c r="V38" s="45" t="str">
+        <x:v>https://annapurnainteractive.com/about</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="36" hidden="0" customHeight="1">
       <x:c r="A39" s="88" t="str">
         <x:v>38</x:v>
       </x:c>
@@ -2768,40 +3333,55 @@
         <x:v>https://www.devolverdigital.com/</x:v>
       </x:c>
       <x:c r="G39" s="44" t="str">
+        <x:v>上市独立游戏发行商；Steam publisher follower 40 万+；premium indie publishing 强品牌。</x:v>
+      </x:c>
+      <x:c r="H39" s="44" t="str">
+        <x:v>Cult of the Lamb, Enter the Gungeon, Hotline Miami, Inscryption, Loop Hero, The Talos Principle, Reigns</x:v>
+      </x:c>
+      <x:c r="I39" s="44" t="str">
+        <x:v>fork@devolverdigital.com; support@devolverdigital.com</x:v>
+      </x:c>
+      <x:c r="J39" s="44" t="str">
+        <x:v>官方 merch/contact 页说明 pitches/CVs 发 fork@，支持发 support@；另有 pitch portal。</x:v>
+      </x:c>
+      <x:c r="K39" s="44" t="str">
         <x:v>独立游戏发行商</x:v>
       </x:c>
-      <x:c r="H39" s="44" t="str">
+      <x:c r="L39" s="44" t="str">
         <x:v>知名独立发行商，更多面向 PC/console premium/indie；不适合当北美移动发行对标。</x:v>
       </x:c>
-      <x:c r="I39" s="44" t="str">
+      <x:c r="M39" s="44" t="str">
         <x:v>除非项目完全转成 premium indie/cozy，不建议优先。</x:v>
       </x:c>
-      <x:c r="J39" s="44" t="str">
+      <x:c r="N39" s="44" t="str">
         <x:v>平台发行；发行合作</x:v>
       </x:c>
-      <x:c r="K39" s="44" t="str">
+      <x:c r="O39" s="44" t="str">
         <x:v>Submissions / publishing</x:v>
       </x:c>
-      <x:c r="L39" s="44" t="str">
+      <x:c r="P39" s="44" t="str">
         <x:v>官网 submissions / LinkedIn</x:v>
       </x:c>
-      <x:c r="M39" s="89" t="str">
+      <x:c r="Q39" s="89" t="str">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="N39" s="44" t="str">
+      <x:c r="R39" s="44" t="str">
         <x:v>观察名单。当前不建议进入现金流救急外联首批。</x:v>
       </x:c>
-      <x:c r="O39" s="44" t="str">
+      <x:c r="S39" s="44" t="str">
         <x:v>https://www.devolverdigital.com/</x:v>
       </x:c>
-      <x:c r="P39" s="44" t="str">
+      <x:c r="T39" s="44" t="str">
         <x:v>https://www.devolverdigital.com/games</x:v>
       </x:c>
-      <x:c r="Q39" s="45" t="str">
+      <x:c r="U39" s="44" t="str">
         <x:v>https://www.devolverdigital.com/contact</x:v>
       </x:c>
-    </x:row>
-    <x:row r="40" ht="24" hidden="0" customHeight="1">
+      <x:c r="V39" s="45" t="str">
+        <x:v>https://merch.devolverdigital.com/pages/contact-us</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="36" hidden="0" customHeight="1">
       <x:c r="A40" s="88" t="str">
         <x:v>39</x:v>
       </x:c>
@@ -2821,40 +3401,55 @@
         <x:v>https://www.tinybuild.com/</x:v>
       </x:c>
       <x:c r="G40" s="44" t="str">
+        <x:v>AIM 上市/多平台发行开发集团；2024 年重组后仍运营多个内部 studio 和外部发行合作。</x:v>
+      </x:c>
+      <x:c r="H40" s="44" t="str">
+        <x:v>Hello Neighbor, Graveyard Keeper, Potion Craft, SpeedRunners, Tinykin, Kill It With Fire, Streets of Rogue</x:v>
+      </x:c>
+      <x:c r="I40" s="44" t="str">
+        <x:v>investorrelations@tinybuild.com</x:v>
+      </x:c>
+      <x:c r="J40" s="44" t="str">
+        <x:v>投资者网站公开 investorrelations@；发行/商务建议官网 Contact/LinkedIn。</x:v>
+      </x:c>
+      <x:c r="K40" s="44" t="str">
         <x:v>中型独立游戏发行/开发集团</x:v>
       </x:c>
-      <x:c r="H40" s="44" t="str">
+      <x:c r="L40" s="44" t="str">
         <x:v>有美国根基的多平台发行/开发集团，行业地位像中型游戏发行公司，但移动 F2P 不是核心。</x:v>
       </x:c>
-      <x:c r="I40" s="44" t="str">
+      <x:c r="M40" s="44" t="str">
         <x:v>如果未来做 PC/console cozy sim，可试；当前移动 Family Island 类适配低。</x:v>
       </x:c>
-      <x:c r="J40" s="44" t="str">
+      <x:c r="N40" s="44" t="str">
         <x:v>发行；IP合作；项目收购可能性低</x:v>
       </x:c>
-      <x:c r="K40" s="44" t="str">
+      <x:c r="O40" s="44" t="str">
         <x:v>Publishing / submissions</x:v>
       </x:c>
-      <x:c r="L40" s="44" t="str">
+      <x:c r="P40" s="44" t="str">
         <x:v>官网 submissions / LinkedIn</x:v>
       </x:c>
-      <x:c r="M40" s="89" t="str">
+      <x:c r="Q40" s="89" t="str">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="N40" s="44" t="str">
+      <x:c r="R40" s="44" t="str">
         <x:v>观察名单。只在产品策略多平台化后触达。</x:v>
       </x:c>
-      <x:c r="O40" s="44" t="str">
+      <x:c r="S40" s="44" t="str">
         <x:v>https://www.tinybuild.com/</x:v>
       </x:c>
-      <x:c r="P40" s="44" t="str">
+      <x:c r="T40" s="44" t="str">
         <x:v>https://www.tinybuild.com/games</x:v>
       </x:c>
-      <x:c r="Q40" s="45" t="str">
+      <x:c r="U40" s="44" t="str">
         <x:v>https://www.tinybuildinvestors.com/</x:v>
       </x:c>
-    </x:row>
-    <x:row r="41" ht="24" hidden="0" customHeight="1">
+      <x:c r="V40" s="45" t="str">
+        <x:v>https://www.tinybuildinvestors.com/regulatory-news</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="36" hidden="0" customHeight="1">
       <x:c r="A41" s="90" t="str">
         <x:v>40</x:v>
       </x:c>
@@ -2874,37 +3469,52 @@
         <x:v>https://about.netflix.com/en/news/games</x:v>
       </x:c>
       <x:c r="G41" s="47" t="str">
+        <x:v>Netflix Games 官网披露 120+ mobile games；Netflix 为全球订阅娱乐平台，游戏是平台内容业务线。</x:v>
+      </x:c>
+      <x:c r="H41" s="47" t="str">
+        <x:v>Cozy Grove: Camp Spirit, Oxenfree, Oxenfree II, Spiritfarer, Into the Breach, Storyteller, GTA Trilogy mobile</x:v>
+      </x:c>
+      <x:c r="I41" s="47" t="str">
+        <x:v>未公开游戏 BD 邮箱；press 使用 Netflix Media Center contact form；Next Games 可用 info@nextgames.com</x:v>
+      </x:c>
+      <x:c r="J41" s="47" t="str">
+        <x:v>Netflix Media Center 不接受 unsolicited materials；如找 Netflix-owned Next Games，可走 info@nextgames.com。</x:v>
+      </x:c>
+      <x:c r="K41" s="47" t="str">
         <x:v>平台型内容买方</x:v>
       </x:c>
-      <x:c r="H41" s="47" t="str">
+      <x:c r="L41" s="47" t="str">
         <x:v>不是传统发行商，但作为平台型内容买方和游戏投资/收购方，可能对 mobile/casual content 有选择性兴趣。</x:v>
       </x:c>
-      <x:c r="I41" s="47" t="str">
+      <x:c r="M41" s="47" t="str">
         <x:v>若项目能服务 Netflix 订阅生态、家庭/cozy 用户或 IP 合作，可作为特殊渠道尝试。</x:v>
       </x:c>
-      <x:c r="J41" s="47" t="str">
+      <x:c r="N41" s="47" t="str">
         <x:v>内容授权；收购；发行/平台合作</x:v>
       </x:c>
-      <x:c r="K41" s="47" t="str">
+      <x:c r="O41" s="47" t="str">
         <x:v>Games content / business development / corporate development</x:v>
       </x:c>
-      <x:c r="L41" s="47" t="str">
+      <x:c r="P41" s="47" t="str">
         <x:v>LinkedIn / warm intro / Netflix games leadership</x:v>
       </x:c>
-      <x:c r="M41" s="91" t="str">
+      <x:c r="Q41" s="91" t="str">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="N41" s="47" t="str">
+      <x:c r="R41" s="47" t="str">
         <x:v>非首批。除非有强引荐或项目可绑定订阅平台逻辑。</x:v>
       </x:c>
-      <x:c r="O41" s="47" t="str">
+      <x:c r="S41" s="47" t="str">
         <x:v>https://about.netflix.com/en/news/games</x:v>
       </x:c>
-      <x:c r="P41" s="47" t="str">
+      <x:c r="T41" s="47" t="str">
         <x:v>https://www.netflix.com/tudum/articles/netflix-games</x:v>
       </x:c>
-      <x:c r="Q41" s="48" t="str">
+      <x:c r="U41" s="47" t="str">
         <x:v>https://jobs.netflix.com/teams/games</x:v>
+      </x:c>
+      <x:c r="V41" s="48" t="str">
+        <x:v>https://media.netflix.com/en/contact-us</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
